--- a/data/sport_artwork_review.BACKUP.xlsx
+++ b/data/sport_artwork_review.BACKUP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E37CDB8-F954-461C-9428-DF69657058C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7710E10D-238A-4D34-8E30-88DFDF25431C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,17 +21,33 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sport-artwork review'!$A$1:$G$1</definedName>
     <definedName name="BilledeValgListe">BilledeListe!$A$1:$A$112</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1917" uniqueCount="535">
   <si>
     <t>Kanalgruppe</t>
   </si>
   <si>
-    <t>Kanal (fra log)</t>
+    <t>Kanaler (alle varianter)</t>
   </si>
   <si>
     <t>Titel</t>
@@ -52,16 +68,838 @@
     <t>A - 3+/TV3 Sport/TV3 Max/Viaplay</t>
   </si>
   <si>
+    <t>TV3+ Denmark (DK,DA).dk; TV3+.dk</t>
+  </si>
+  <si>
+    <t>Ace Ventura - detektiv</t>
+  </si>
+  <si>
+    <t>(intet billede)</t>
+  </si>
+  <si>
+    <t>Ignorer</t>
+  </si>
+  <si>
+    <t>TV3+ HD (D) (T).dk; TV3+.dk</t>
+  </si>
+  <si>
+    <t>Ace Ventura: Pet Detective</t>
+  </si>
+  <si>
+    <t>TV3 MAX HD (D) (T).dk; TV3 Max Denmark (DK,DA).dk; TV3 Max.dk</t>
+  </si>
+  <si>
+    <t>Ax Men</t>
+  </si>
+  <si>
+    <t>TV3+ Denmark (DK,DA).dk; TV3+ HD (D) (T).dk; TV3+.dk</t>
+  </si>
+  <si>
+    <t>Bad Boys</t>
+  </si>
+  <si>
+    <t>Bad Boys for Life</t>
+  </si>
+  <si>
+    <t>Bad Boys For Life</t>
+  </si>
+  <si>
+    <t>Bad Boys II</t>
+  </si>
+  <si>
+    <t>Forsvundet sporløst</t>
+  </si>
+  <si>
+    <t>Hawaii Five-0</t>
+  </si>
+  <si>
+    <t>Ice Road Truckers</t>
+  </si>
+  <si>
+    <t>TV3 Max Denmark (DK,DA).dk; TV3 Max.dk</t>
+  </si>
+  <si>
+    <t>Lost Gold of World War II</t>
+  </si>
+  <si>
+    <t>Max Anger - With One Eye Open</t>
+  </si>
+  <si>
+    <t>Mountain Men</t>
+  </si>
+  <si>
+    <t>NCIS</t>
+  </si>
+  <si>
+    <t>NCIS: Hawai'i</t>
+  </si>
+  <si>
+    <t>NCIS: Los Angeles</t>
+  </si>
+  <si>
+    <t>Pacific Blue</t>
+  </si>
+  <si>
+    <t>Paranormal Caught on Camera</t>
+  </si>
+  <si>
+    <t>Pawn Stars</t>
+  </si>
+  <si>
+    <t>Rustbunker og restaurering</t>
+  </si>
+  <si>
+    <t>S.W.A.T.</t>
+  </si>
+  <si>
+    <t>TV3 MAX HD (D) (T).dk; TV3 Max Denmark (DK,DA).dk; TV3 Max.dk; TV3+ Denmark (DK,DA).dk; TV3+ HD (D) (T).dk; TV3+.dk</t>
+  </si>
+  <si>
+    <t>Shipping Wars</t>
+  </si>
+  <si>
+    <t>Simpsons</t>
+  </si>
+  <si>
+    <t>Skrotjægerne</t>
+  </si>
+  <si>
+    <t>The American Runestone</t>
+  </si>
+  <si>
+    <t>The Last Son</t>
+  </si>
+  <si>
+    <t>The Simpsons</t>
+  </si>
+  <si>
+    <t>B - TV2 Sport/TV2 Sport X/TV2</t>
+  </si>
+  <si>
+    <t>TV 2 HD (D) (T).dk; TV 2.dk</t>
+  </si>
+  <si>
+    <t>12 News</t>
+  </si>
+  <si>
+    <t>17 News</t>
+  </si>
+  <si>
+    <t>18 News</t>
+  </si>
+  <si>
+    <t>19 News</t>
+  </si>
+  <si>
+    <t>America's Got Talent</t>
+  </si>
+  <si>
+    <t>Arlington Road</t>
+  </si>
+  <si>
+    <t>C - DR1/DR2</t>
+  </si>
+  <si>
+    <t>DR1 Denmark (DK,DA).dk; DR1 HD (T).dk; DR1.dk; dr1.dk</t>
+  </si>
+  <si>
+    <t>Aftenshowet</t>
+  </si>
+  <si>
+    <t>DR1 Denmark (DK,DA).dk; DR1 HD (T).dk; DR1.dk</t>
+  </si>
+  <si>
+    <t>Alene i vildmarken USA</t>
+  </si>
+  <si>
+    <t>DR1.dk; dr1.dk</t>
+  </si>
+  <si>
+    <t>Alene i vildmarken USA XI (2:12)</t>
+  </si>
+  <si>
+    <t>Alene i vildmarken USA XI (3:12)</t>
+  </si>
+  <si>
+    <t>DR2.dk</t>
+  </si>
+  <si>
+    <t>Alt forladt</t>
+  </si>
+  <si>
+    <t>DR2 Denmark (DK,DA).dk; DR2 HD (T).dk; DR2.dk</t>
+  </si>
+  <si>
+    <t>Alt forladt - Elhøj og Kirckhoff i det glemte Danmark</t>
+  </si>
+  <si>
+    <t>DR2.dk; dr2.dk</t>
+  </si>
+  <si>
+    <t>Alt forladt - Sindssygehospitalet</t>
+  </si>
+  <si>
+    <t>Ambulance</t>
+  </si>
+  <si>
+    <t>Antikkrejlerne med kendisser</t>
+  </si>
+  <si>
+    <t>Antikkrejlerne med kendisser (215)</t>
+  </si>
+  <si>
+    <t>Antikkrejlerne med kendisser (220)</t>
+  </si>
+  <si>
+    <t>DR1.dk</t>
+  </si>
+  <si>
+    <t>Belgravia</t>
+  </si>
+  <si>
+    <t>Belgravia: Det næste kapitel (3:8)</t>
+  </si>
+  <si>
+    <t>Belgravia: Det næste kapitel (4:8)</t>
+  </si>
+  <si>
+    <t>Belgravia: Det næste kapitel (5:8)</t>
+  </si>
+  <si>
+    <t>Belgravia: The Next Chapter</t>
+  </si>
+  <si>
+    <t>Berlusconi</t>
+  </si>
+  <si>
+    <t>Bjerget</t>
+  </si>
+  <si>
+    <t>Bjerget (3:12)</t>
+  </si>
+  <si>
+    <t>Bjerget (4:12)</t>
+  </si>
+  <si>
+    <t>Boligfix for nul og niks</t>
+  </si>
+  <si>
+    <t>Boligfix for nul og niks: Fra livskrise til børnelatter</t>
+  </si>
+  <si>
+    <t>DR2 Denmark (DK,DA).dk; DR2 HD (T).dk; DR2.dk; dr2.dk</t>
+  </si>
+  <si>
+    <t>Burnt</t>
+  </si>
+  <si>
+    <t>Copenhagen Design</t>
+  </si>
+  <si>
+    <t>De frivillige</t>
+  </si>
+  <si>
+    <t>DR2 Denmark (DK,DA).dk; dr2.dk</t>
+  </si>
+  <si>
+    <t>Deadline</t>
+  </si>
+  <si>
+    <t>Deadline: Forstår vi Mellemøsten?</t>
+  </si>
+  <si>
+    <t>Deadline: Krasniks liberale længsel</t>
+  </si>
+  <si>
+    <t>Deadline: Vanopslaghs usynlige ånd</t>
+  </si>
+  <si>
+    <t>Deadline: Zelenskyj under pres</t>
+  </si>
+  <si>
+    <t>Der kan man se</t>
+  </si>
+  <si>
+    <t>Der kan man se (7:16)</t>
+  </si>
+  <si>
+    <t>Der kan man se (8:16)</t>
+  </si>
+  <si>
+    <t>Det bli'r ikke bedre</t>
+  </si>
+  <si>
+    <t>Dreyers skygger</t>
+  </si>
+  <si>
+    <t>Dronningeriget (4:4) Dorothea</t>
+  </si>
+  <si>
+    <t>DRs bedste - kort fortalt</t>
+  </si>
+  <si>
+    <t>DRs bedste - kort fortalt: Sport og hjælp</t>
+  </si>
+  <si>
+    <t>Drømmen om et liv på landet</t>
+  </si>
+  <si>
+    <t>Drømmen om et liv på landet (2:6)</t>
+  </si>
+  <si>
+    <t>Er der en arkitekt til stede?</t>
+  </si>
+  <si>
+    <t>Er der en arkitekt til stede? (4:4) - Den fallerede fremtidsby</t>
+  </si>
+  <si>
+    <t>Europas vidundere</t>
+  </si>
+  <si>
+    <t>Europas vidundere III Sacré-Cæur</t>
+  </si>
+  <si>
+    <t>Ferie, ferie, ferie</t>
+  </si>
+  <si>
+    <t>Ferie, ferie, ferie: Camping</t>
+  </si>
+  <si>
+    <t>Flugten fra Bolivia</t>
+  </si>
+  <si>
+    <t>Flugten fra Bolivia (3:6)</t>
+  </si>
+  <si>
+    <t>Flugten fra Bolivia (4:6)</t>
+  </si>
+  <si>
+    <t>Flådens historie</t>
+  </si>
+  <si>
+    <t>Flådens historie (6:7)</t>
+  </si>
+  <si>
+    <t>Flådens historie (7:7)</t>
+  </si>
+  <si>
+    <t>Frank &amp; Kastaniegaarden</t>
+  </si>
+  <si>
+    <t>Frank &amp; Kastaniegaarden - Sisyfos Karpedam</t>
+  </si>
+  <si>
+    <t>dr1.dk</t>
+  </si>
+  <si>
+    <t>Frank And Kastaniegaarden - Sisyfos Karpedam</t>
+  </si>
+  <si>
+    <t>FredagsTamTam</t>
+  </si>
+  <si>
+    <t>dr2.dk</t>
+  </si>
+  <si>
+    <t>Fukushima - et atomkraftsmareridt</t>
+  </si>
+  <si>
+    <t>Full Metal Jacket</t>
+  </si>
+  <si>
+    <t>Før fyraften</t>
+  </si>
+  <si>
+    <t>Før Søndagen</t>
+  </si>
+  <si>
+    <t>Før søndagen</t>
+  </si>
+  <si>
+    <t>Før søndagen: Vi pløjed og vi så'de</t>
+  </si>
+  <si>
+    <t>Giv os naturen tilbage</t>
+  </si>
+  <si>
+    <t>Giv os naturen tilbage II (7:8)</t>
+  </si>
+  <si>
+    <t>Hammerslag</t>
+  </si>
+  <si>
+    <t>Hammerslag 2021</t>
+  </si>
+  <si>
+    <t>Hammerslag 2021 - Historiske huse</t>
+  </si>
+  <si>
+    <t>Huset på Christianshavn</t>
+  </si>
+  <si>
+    <t>Huset på Christianshavn (32) Formand Olsen</t>
+  </si>
+  <si>
+    <t>Huset på Christianshavn Formand Olsen</t>
+  </si>
+  <si>
+    <t>Husker du ... årtierne</t>
+  </si>
+  <si>
+    <t>Husker du...</t>
+  </si>
+  <si>
+    <t>Husker du... 1988</t>
+  </si>
+  <si>
+    <t>Husmorens storhed og fald</t>
+  </si>
+  <si>
+    <t>Husmorens storhed og fald (2:4)</t>
+  </si>
+  <si>
+    <t>Hvad tror danskerne på</t>
+  </si>
+  <si>
+    <t>Hvad tror danskerne på: Karma, overtro eller Gud</t>
+  </si>
+  <si>
+    <t>Hvad tror danskerne på: Karma, overtro eller Gud?</t>
+  </si>
+  <si>
+    <t>Hvornår var det nu det var</t>
+  </si>
+  <si>
+    <t>Hvornår var det nu det var (1:17)</t>
+  </si>
+  <si>
+    <t>Ingen kender dagen</t>
+  </si>
+  <si>
+    <t>DR2 Denmark (DK,DA).dk; DR2 HD (T).dk</t>
+  </si>
+  <si>
+    <t>Italien med Stanley Tucci</t>
+  </si>
+  <si>
+    <t>Jack the Ripper - Skrevet med blod (2:3)</t>
+  </si>
+  <si>
+    <t>Jordemoderen</t>
+  </si>
+  <si>
+    <t>Jordemoderen XI (8:8)</t>
+  </si>
+  <si>
+    <t>Kender du typen?</t>
+  </si>
+  <si>
+    <t>Kender Du Typen? 2018</t>
+  </si>
+  <si>
+    <t>Kender Du Typen? 2018 - Med flygel og bjælkehytte</t>
+  </si>
+  <si>
+    <t>Kommissionen</t>
+  </si>
+  <si>
+    <t>Kontant</t>
+  </si>
+  <si>
+    <t>Kontant: De fynske flex-konger</t>
+  </si>
+  <si>
+    <t>Kontant: Flextrafik på slingrekurs</t>
+  </si>
+  <si>
+    <t>Kriminalinspektør Banks</t>
+  </si>
+  <si>
+    <t>Kriminalinspektør Banks: Djævelens ven</t>
+  </si>
+  <si>
+    <t>Kriminalinspektør Banks: Kold er graven</t>
+  </si>
+  <si>
+    <t>Kriminalinspektør Banks: Uskyldige grave</t>
+  </si>
+  <si>
+    <t>Kunstnerkolonien</t>
+  </si>
+  <si>
+    <t>Kvissen</t>
+  </si>
+  <si>
+    <t>Kvissen (15:16)</t>
+  </si>
+  <si>
+    <t>Løvens hule junior</t>
+  </si>
+  <si>
+    <t>Løvens hule junior (2:6) Aldrig mere hundebæ under skoene</t>
+  </si>
+  <si>
+    <t>Løvens hule junior (2:6) Aldrig mere hundebæ under skoene!</t>
+  </si>
+  <si>
+    <t>Løvens hule junior Aldrig mere hundebæ under skoene!</t>
+  </si>
+  <si>
+    <t>Mayafolkets tabte verden</t>
+  </si>
+  <si>
+    <t>Mayafolkets tabte verden (1:2)</t>
+  </si>
+  <si>
+    <t>Mayafolkets tabte verden (2:2)</t>
+  </si>
+  <si>
+    <t>Mennesket</t>
+  </si>
+  <si>
+    <t>Mennesket (3:5)</t>
+  </si>
+  <si>
+    <t>Mississippi i fortidens skygge</t>
+  </si>
+  <si>
+    <t>Morgenandagten</t>
+  </si>
+  <si>
+    <t>DR2 Denmark (DK,DA).dk</t>
+  </si>
+  <si>
+    <t>Mysteriet om den forsvundne svindlerdronning</t>
+  </si>
+  <si>
+    <t>Mysteriet om den forsvundne svindlerdronning (1:3)</t>
+  </si>
+  <si>
+    <t>Nak &amp; Æd</t>
+  </si>
+  <si>
+    <t>Nak &amp; Æd - en uvak i Grønland (10:10)</t>
+  </si>
+  <si>
+    <t>Nak And Æd - en uvak i Grønland (10:10)</t>
+  </si>
+  <si>
+    <t>Naturfotografen</t>
+  </si>
+  <si>
+    <t>Naturfotografen II (4:10)</t>
+  </si>
+  <si>
+    <t>Naturfotografen II (5:10)</t>
+  </si>
+  <si>
+    <t>Nicole Kidman - Australier i Hollywood</t>
+  </si>
+  <si>
+    <t>OBS</t>
+  </si>
+  <si>
+    <t>Optur</t>
+  </si>
+  <si>
+    <t>Optur (3:6) - Over grænsen i Sønderjylland</t>
+  </si>
+  <si>
+    <t>Otte dage for Rom</t>
+  </si>
+  <si>
+    <t>Otte dage, der skabte Rom (2:8) Spartacus' oprør</t>
+  </si>
+  <si>
+    <t>Otte dage, der skabte Rom Spartacus' oprør</t>
+  </si>
+  <si>
+    <t>P2 Radioavisen</t>
+  </si>
+  <si>
+    <t>P3 Essensen</t>
+  </si>
+  <si>
+    <t>P3 Essensen: AI overtager måske dit job hurtigere end du tror</t>
+  </si>
+  <si>
+    <t>På skuldrene af H. C. Ørsted</t>
+  </si>
+  <si>
+    <t>På skuldrene af H. C. Ørsted - Hvor meget vejer et kilo egentligt</t>
+  </si>
+  <si>
+    <t>På skuldrene af H. C. Ørsted - Hvor meget vejer et kilo egentligt?</t>
+  </si>
+  <si>
+    <t>Radioavisen</t>
+  </si>
+  <si>
+    <t>Red Rock West</t>
+  </si>
+  <si>
+    <t>RO PÅ i naturen</t>
+  </si>
+  <si>
+    <t>RO PÅ med DR Symfoniorkestret</t>
+  </si>
+  <si>
+    <t>RO PÅ med DR Symfoniorkestret: I vandkanten</t>
+  </si>
+  <si>
+    <t>DR1.dk; DR2.dk; dr1.dk; dr2.dk</t>
+  </si>
+  <si>
+    <t>Seneste nyt fra TVA</t>
+  </si>
+  <si>
+    <t>Seneste nyt fra TVA - Del 1/2</t>
+  </si>
+  <si>
+    <t>Seneste nyt fra TVA - Del 2/2</t>
+  </si>
+  <si>
+    <t>Shetland</t>
+  </si>
+  <si>
+    <t>Shetland IX (3:6)</t>
+  </si>
+  <si>
+    <t>Signe Moldes Roadshow</t>
+  </si>
+  <si>
+    <t>Signe Moldes Roadshow: Brande</t>
+  </si>
+  <si>
+    <t>Skattejægerne</t>
+  </si>
+  <si>
+    <t>Skattejægerne (1:10)</t>
+  </si>
+  <si>
+    <t>Smagen af Italien</t>
+  </si>
+  <si>
+    <t>Smagen af Italien (2:6)</t>
+  </si>
+  <si>
+    <t>Smilehullet</t>
+  </si>
+  <si>
+    <t>Smilehullet: Dirch danser med Sonja Oppenhagen</t>
+  </si>
+  <si>
+    <t>Solens mad</t>
+  </si>
+  <si>
+    <t>Solens mad (3:6)</t>
+  </si>
+  <si>
+    <t>Sommeren</t>
+  </si>
+  <si>
+    <t>Sommeren 1985</t>
+  </si>
+  <si>
+    <t>Sommeren 1985 (4:6)</t>
+  </si>
+  <si>
+    <t>Store danskere</t>
+  </si>
+  <si>
+    <t>Store danskere - Gunnar Nu Hansen</t>
+  </si>
+  <si>
+    <t>Søren Vester bygger sommerhus</t>
+  </si>
+  <si>
+    <t>Søren Vester bygger sommerhus (2:8): I mit hoved er vi faktisk færdige</t>
+  </si>
+  <si>
+    <t>Team Bachstad</t>
+  </si>
+  <si>
+    <t>Team Bachstad i Japan</t>
+  </si>
+  <si>
+    <t>Team Bachstad i Japan (5:9)</t>
+  </si>
+  <si>
+    <t>Tegnsprogsmagasinet Udsyn</t>
+  </si>
+  <si>
+    <t>Terror ved Olympiaden (2:3)</t>
+  </si>
+  <si>
+    <t>The Quiet Girl</t>
+  </si>
+  <si>
+    <t>The Report</t>
+  </si>
+  <si>
+    <t>Trumps USA</t>
+  </si>
+  <si>
+    <t>DR1 Denmark (DK,DA).dk; DR1 HD (T).dk; DR1.dk; DR2 Denmark (DK,DA).dk; DR2 HD (T).dk; DR2.dk; dr1.dk; dr2.dk</t>
+  </si>
+  <si>
+    <t>TVA</t>
+  </si>
+  <si>
+    <t>Udsendelsesophør</t>
+  </si>
+  <si>
+    <t>Uforglemt</t>
+  </si>
+  <si>
+    <t>Uforglemt: Mordet på Hayley Reid (1:3)</t>
+  </si>
+  <si>
+    <t>Vera</t>
+  </si>
+  <si>
+    <t>Vera: Mørk vej</t>
+  </si>
+  <si>
+    <t>Vera: Skygger på himlen</t>
+  </si>
+  <si>
+    <t>Vilde eventyr</t>
+  </si>
+  <si>
+    <t>Vilde eventyr (1)</t>
+  </si>
+  <si>
+    <t>Vilde eventyr - med Vicky og Rane</t>
+  </si>
+  <si>
+    <t>Vilde haver - gør det selv</t>
+  </si>
+  <si>
+    <t>Vilde haver - gør det selv: Sådan indsamler du blomsterfrø i naturen</t>
+  </si>
+  <si>
+    <t>Vores vejr</t>
+  </si>
+  <si>
+    <t>Vores Vejr</t>
+  </si>
+  <si>
+    <t>Vores år</t>
+  </si>
+  <si>
+    <t>Vores år (2:4)</t>
+  </si>
+  <si>
+    <t>We Live in Time</t>
+  </si>
+  <si>
+    <t>Ørneborgen</t>
+  </si>
+  <si>
+    <t>Bolighaj finder hjem</t>
+  </si>
+  <si>
+    <t>CPH Lufthavnen</t>
+  </si>
+  <si>
+    <t>TV 2 Sport Denmark (DK,DA).dk; TV 2 Sport HD (D) (T).dk; TV 2 Sport.dk</t>
+  </si>
+  <si>
+    <t>Cykling: Vuelta a España</t>
+  </si>
+  <si>
+    <t>Cykling-generic.jpg</t>
+  </si>
+  <si>
+    <t>Danmarks dummeste</t>
+  </si>
+  <si>
+    <t>De ødelagte heste</t>
+  </si>
+  <si>
+    <t>Fear Factor</t>
+  </si>
+  <si>
+    <t>Forræder</t>
+  </si>
+  <si>
+    <t>Forræder - Under kutten</t>
+  </si>
+  <si>
+    <t>Go' aften Live</t>
+  </si>
+  <si>
+    <t>Go' morgen Danmark</t>
+  </si>
+  <si>
+    <t>Grænsepatruljen Canada</t>
+  </si>
+  <si>
+    <t>Han, hun og haven</t>
+  </si>
+  <si>
+    <t>John Wick: Chapter 2</t>
+  </si>
+  <si>
+    <t>Klipfiskerne</t>
+  </si>
+  <si>
+    <t>Kurs mod fjerne kyster</t>
+  </si>
+  <si>
+    <t>Linde på Langeland</t>
+  </si>
+  <si>
+    <t>Motorvejspatruljen</t>
+  </si>
+  <si>
+    <t>Nikolai</t>
+  </si>
+  <si>
+    <t>Nyhederne og Vejret</t>
+  </si>
+  <si>
+    <t>Nyhederne, Sporten og Vejret</t>
+  </si>
+  <si>
+    <t>Regionale nyheder</t>
+  </si>
+  <si>
+    <t>Regionalprogram</t>
+  </si>
+  <si>
+    <t>Rita</t>
+  </si>
+  <si>
+    <t>TV 2 Sport HD (D) (T).dk</t>
+  </si>
+  <si>
+    <t>Sendeophold</t>
+  </si>
+  <si>
     <t>TV3 Sport HD (D) (T).dk</t>
   </si>
   <si>
     <t>1. Division</t>
   </si>
   <si>
-    <t>(kanal-fallback)</t>
-  </si>
-  <si>
-    <t>TV3 Sport Denmark (DK,DA).dk</t>
+    <t>tv3sport-generic.jpg</t>
+  </si>
+  <si>
+    <t>Betinia Liga.jpg</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>1. Division Magasinet</t>
+  </si>
+  <si>
+    <t>TMDb</t>
+  </si>
+  <si>
+    <t>TV3 Sport Denmark (DK,DA).dk; TV3 Sport HD (D) (T).dk; TV3 Sport.dk</t>
   </si>
   <si>
     <t>1. Division Studie</t>
@@ -76,46 +914,55 @@
     <t>1. Division: AaB - HB Køge</t>
   </si>
   <si>
-    <t>TV3 Max Denmark (DK,DA).dk</t>
+    <t>TV3 Max Denmark (DK,DA).dk; TV3 Max.dk; TV3 Sport Denmark (DK,DA).dk; TV3 Sport.dk</t>
   </si>
   <si>
     <t>3F Superliga</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/flanaganz/epgoal/main/Sport/Fodbold.jpg</t>
-  </si>
-  <si>
     <t>3F Superliga.jpg</t>
   </si>
   <si>
-    <t>X</t>
+    <t>TV3 MAX HD (D) (T).dk</t>
+  </si>
+  <si>
+    <t>3F Superliga: AC Horsens - Viborg FF</t>
+  </si>
+  <si>
+    <t>TV3 Sport Denmark (DK,DA).dk; TV3 Sport.dk</t>
+  </si>
+  <si>
+    <t>Betinia LIGA</t>
+  </si>
+  <si>
+    <t>Betinia LIGA Magasinet</t>
+  </si>
+  <si>
+    <t>Bundesliga Fodbold</t>
+  </si>
+  <si>
+    <t>Fodbold.jpg</t>
+  </si>
+  <si>
+    <t>Bundesliga Fodbold.jpg</t>
+  </si>
+  <si>
+    <t>Bundesliga Fodbold: Bayern München - Stuttgart</t>
+  </si>
+  <si>
+    <t>Bundesliga Fodbold: Dortmund - Hamburger SV</t>
   </si>
   <si>
     <t>TV3 Max.dk</t>
   </si>
   <si>
-    <t>TV3 MAX HD (D) (T).dk</t>
-  </si>
-  <si>
-    <t>3F Superliga: AC Horsens - Viborg FF</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold.jpg</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold: Bayern München - Stuttgart</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold: Dortmund - Hamburger SV</t>
-  </si>
-  <si>
     <t>Bundesliga: Bayern München - Stuttgart</t>
   </si>
   <si>
-    <t>https://raw.githubusercontent.com/flanaganz/epgoal/main/Sport/Tennis%20ATP%20500.jpg</t>
+    <t>Tennis ATP 500.jpg</t>
+  </si>
+  <si>
+    <t>Bundesliga: Dortmund - Hamburger SV</t>
   </si>
   <si>
     <t>Champions League Weekly</t>
@@ -124,6 +971,9 @@
     <t>Champions League Weekly.jpg</t>
   </si>
   <si>
+    <t>TV3 MAX HD (D) (T).dk; TV3 Max.dk</t>
+  </si>
+  <si>
     <t>Champions League Weekly: UEFA Champions League Weekly</t>
   </si>
   <si>
@@ -133,24 +983,99 @@
     <t>Danskerklubben</t>
   </si>
   <si>
+    <t>https://i-viaplay-com.akamaized.net/viaplay-prod/155/944/Sport_News1920x1080_SportNews_ok.jpg</t>
+  </si>
+  <si>
+    <t>Discover a Club</t>
+  </si>
+  <si>
+    <t>EFL Championship</t>
+  </si>
+  <si>
+    <t>EFL Championship Highligts.jpg</t>
+  </si>
+  <si>
+    <t>EFL Championship: Middlesbrough - West Bromwich</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Formel 1.jpg</t>
+  </si>
+  <si>
     <t>F1: Hollands Grand Prix - Løbet</t>
   </si>
   <si>
-    <t>Formel 1.jpg</t>
-  </si>
-  <si>
     <t>Fodbold: Premier League-studiet</t>
   </si>
   <si>
+    <t>Premier League.jpg</t>
+  </si>
+  <si>
+    <t>Formel 1</t>
+  </si>
+  <si>
+    <t>Formel 1 360°</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/uzNsBqsMSkKyL4bbatvCvYYpDOj.jpg</t>
+  </si>
+  <si>
+    <t>Formel 1 360°: Formel 1 360°</t>
+  </si>
+  <si>
+    <t>Viaplay Sport News HD (D) (T).dk; Viaplay Sport News.dk</t>
+  </si>
+  <si>
+    <t>Før Superligaen</t>
+  </si>
+  <si>
+    <t>Højdepunkter fra EFL Championship</t>
+  </si>
+  <si>
+    <t>IndyCar</t>
+  </si>
+  <si>
+    <t>IndyCar.jpg</t>
+  </si>
+  <si>
+    <t>IndyCar: Freedom 250 Grand Prix of Washington, D.C.</t>
+  </si>
+  <si>
+    <t>IndyCar: Snap-On Makers and Fixers 250 - Løb 1</t>
+  </si>
+  <si>
+    <t>TV3 MAX HD (D) (T).dk; TV3 Max Denmark (DK,DA).dk; TV3 Max.dk; TV3 Sport Denmark (DK,DA).dk; TV3 Sport HD (D) (T).dk; TV3 Sport.dk; Viaplay Sport News HD (D) (T).dk; Viaplay Sport News.dk</t>
+  </si>
+  <si>
+    <t>Let’s Be Frank</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/tzcEiG73S5a9HtMflMQ0Z8WWms.jpg</t>
+  </si>
+  <si>
+    <t>Let’s Be Frank: Let's be Frank</t>
+  </si>
+  <si>
+    <t>TV3 Max Denmark (DK,DA).dk; TV3 Max.dk; TV3 Sport Denmark (DK,DA).dk; TV3 Sport HD (D) (T).dk; TV3 Sport.dk</t>
+  </si>
+  <si>
     <t>PDC European Tour</t>
   </si>
   <si>
     <t>PDC World Series of Darts.jpg</t>
   </si>
   <si>
+    <t>TV3 MAX HD (D) (T).dk; TV3 Max.dk; TV3 Sport.dk</t>
+  </si>
+  <si>
     <t>PDC European Tour: Hungarian Darts Trophy</t>
   </si>
   <si>
+    <t>TV3 Max Denmark (DK,DA).dk; TV3 Max.dk; Viaplay Sport News HD (D) (T).dk; Viaplay Sport News.dk</t>
+  </si>
+  <si>
     <t>Premier League</t>
   </si>
   <si>
@@ -166,13 +1091,49 @@
     <t>Premier League: Tottenham - Newcastle</t>
   </si>
   <si>
-    <t>Viaplay Sport News HD (D) (T).dk</t>
+    <t>Sky Sports: Soccer Saturday</t>
+  </si>
+  <si>
+    <t>https://image.tmdb.org/t/p/original/rIl1pgmuVBwBbDqS5w3hVD8Z9UW.jpg</t>
+  </si>
+  <si>
+    <t>Sky Sports: The Football Show</t>
+  </si>
+  <si>
+    <t>Sky Sports The Football Show.jpg</t>
   </si>
   <si>
     <t>Sky Sports: Total Football</t>
   </si>
   <si>
-    <t>Sky Sports The Football Show.jpg</t>
+    <t>Sport News</t>
+  </si>
+  <si>
+    <t>TV3 Sport Denmark (DK,DA).dk; TV3 Sport HD (D) (T).dk; TV3 Sport.dk; Viaplay Sport News HD (D) (T).dk; Viaplay Sport News.dk</t>
+  </si>
+  <si>
+    <t>Sportstalk</t>
+  </si>
+  <si>
+    <t>Superliga</t>
+  </si>
+  <si>
+    <t>Superliga Studie</t>
+  </si>
+  <si>
+    <t>Superliga Studiet.jpg</t>
+  </si>
+  <si>
+    <t>Superliga Studie: AC Horsens - Viborg FF</t>
+  </si>
+  <si>
+    <t>TV3 Sport Denmark (DK,DA).dk; TV3 Sport.dk; Viaplay Sport News HD (D) (T).dk; Viaplay Sport News.dk</t>
+  </si>
+  <si>
+    <t>Superliga Studiet</t>
+  </si>
+  <si>
+    <t>TV3 Max.dk; TV3 Sport.dk</t>
   </si>
   <si>
     <t>Superliga: AC Horsens - Viborg FF</t>
@@ -181,7 +1142,16 @@
     <t>SuperligaTilsynet</t>
   </si>
   <si>
-    <t>TMDb</t>
+    <t>Superligatilsynet.jpg</t>
+  </si>
+  <si>
+    <t>SuperligaTilsynet: SuperligaTilsynet: Luis Binks svarer tilbage og FCK kollapser</t>
+  </si>
+  <si>
+    <t>TV3 Sport HD (D) (T).dk; TV3 Sport.dk; Viaplay Sport News HD (D) (T).dk; Viaplay Sport News.dk</t>
+  </si>
+  <si>
+    <t>Var-Rummet</t>
   </si>
   <si>
     <t>Watt the F1!?</t>
@@ -193,12 +1163,81 @@
     <t>Watt the F1!?: Watt The F1!?: Ny Ferrari-fadæse</t>
   </si>
   <si>
-    <t>B - TV2 Sport/TV2 Sport X/TV2</t>
+    <t>TV 2 Sport X.dk</t>
+  </si>
+  <si>
+    <t>A-Liga: Brøndby IF-F.C. København</t>
+  </si>
+  <si>
+    <t>A-Liga.jpg</t>
+  </si>
+  <si>
+    <t>A-Liga: Efter Brøndby IF-F.C. København</t>
+  </si>
+  <si>
+    <t>A-Liga: FC Midtjylland-ASA, Aarhus</t>
+  </si>
+  <si>
+    <t>A-Liga: FC Nordsjælland-F.C. København</t>
+  </si>
+  <si>
+    <t>A-Liga: Før Brøndby IF-F.C. København</t>
+  </si>
+  <si>
+    <t>A-Liga: Målfesten</t>
+  </si>
+  <si>
+    <t>AftenVuelta</t>
+  </si>
+  <si>
+    <t>AftenVuelta.jpg</t>
   </si>
   <si>
     <t>TV 2 Sport.dk</t>
   </si>
   <si>
+    <t>Amerikansk fodbold: Nordic Storm-Munich Ravens, finale</t>
+  </si>
+  <si>
+    <t>NFL.jpg</t>
+  </si>
+  <si>
+    <t>TV 2 Sport X Denmark (DK,DA).dk; TV 2 Sport X HD (D) (T).dk; TV 2 Sport X.dk</t>
+  </si>
+  <si>
+    <t>Atletik: Diamond League</t>
+  </si>
+  <si>
+    <t>Atletik Diamond League.jpg</t>
+  </si>
+  <si>
+    <t>Atletik: Diamond League, Zürich</t>
+  </si>
+  <si>
+    <t>Beliggenhed, beliggenhed, beliggenhed</t>
+  </si>
+  <si>
+    <t>Cykling: Vuelta a España - Studiet</t>
+  </si>
+  <si>
+    <t>Vuelta a España.jpeg</t>
+  </si>
+  <si>
+    <t>Fodbold: A Liga (k) - Studiet</t>
+  </si>
+  <si>
+    <t>Fodbold: A-Liga (k) - Kampe</t>
+  </si>
+  <si>
+    <t>Fodbold: A-Liga (k) - Målfesten</t>
+  </si>
+  <si>
+    <t>Fodbold: Serie A</t>
+  </si>
+  <si>
+    <t>Serie A.jpg</t>
+  </si>
+  <si>
     <t>Herreligaen: GOG-Skjern</t>
   </si>
   <si>
@@ -211,13 +1250,16 @@
     <t>Herreligaen: TTH Holstebro - Bjerringbro-Silkeborg</t>
   </si>
   <si>
-    <t>TV 2 Sport Denmark (DK,DA).dk</t>
+    <t>TV 2 HD (D) (T).dk; TV 2 Sport Denmark (DK,DA).dk; TV 2 Sport HD (D) (T).dk; TV 2 Sport.dk; TV 2.dk</t>
   </si>
   <si>
     <t>Håndbold (m): Håndboldligaen - Kampe</t>
   </si>
   <si>
-    <t>TV 2 Sport HD (D) (T).dk</t>
+    <t>Håndbold: Liga Håndbold - studiet</t>
+  </si>
+  <si>
+    <t>Håndbold Herreligaen.jpg</t>
   </si>
   <si>
     <t>Kvindeligaen</t>
@@ -229,16 +1271,22 @@
     <t>Kvindeligaen: Ikast-Odense</t>
   </si>
   <si>
+    <t>TV 2 Sport Denmark (DK,DA).dk; TV 2 Sport HD (D) (T).dk; TV 2 Sport X Denmark (DK,DA).dk; TV 2 Sport X HD (D) (T).dk; TV 2 Sport X.dk; TV 2 Sport.dk</t>
+  </si>
+  <si>
     <t>Mountainbike: World Cup</t>
   </si>
   <si>
-    <t>TV 2 Sport X Denmark (DK,DA).dk</t>
-  </si>
-  <si>
-    <t>TV 2 Sport X HD (D) (T).dk</t>
-  </si>
-  <si>
-    <t>TV 2 Sport X.dk</t>
+    <t>VM i MTB.jpg</t>
+  </si>
+  <si>
+    <t>NFL</t>
+  </si>
+  <si>
+    <t>NFL: Cleveland Browns-New England Patriots, pre-season</t>
+  </si>
+  <si>
+    <t>NFL: Philadelphia Eagles-Cincinnati Bengals, pre-season</t>
   </si>
   <si>
     <t>Serie A: AC Milan-Venezia</t>
@@ -250,6 +1298,18 @@
     <t>Serie A: Juventus-Parma</t>
   </si>
   <si>
+    <t>Sporten</t>
+  </si>
+  <si>
+    <t>Sporten.jpg</t>
+  </si>
+  <si>
+    <t>The Father</t>
+  </si>
+  <si>
+    <t>The Wedding Date</t>
+  </si>
+  <si>
     <t>VM i MTB: Elite cross-country, short track (k)</t>
   </si>
   <si>
@@ -262,7 +1322,25 @@
     <t>VM i MTB: Elite, Downhill, elite (m)</t>
   </si>
   <si>
-    <t>A-Liga.jpg</t>
+    <t>Vuelta a España: 6. etape</t>
+  </si>
+  <si>
+    <t>Vuelta a España: 7. etape</t>
+  </si>
+  <si>
+    <t>Vuelta a España: 8. etape</t>
+  </si>
+  <si>
+    <t>Vuelta a España: Studiet</t>
+  </si>
+  <si>
+    <t>WTA: Tauson-Parry, kvartfinale, Monterrey</t>
+  </si>
+  <si>
+    <t>WTA-generic.jpeg</t>
+  </si>
+  <si>
+    <t>WTA-generic.jpg</t>
   </si>
   <si>
     <t>ATP Tour Highlights.jpg</t>
@@ -277,21 +1355,12 @@
     <t>Aften Roubaix.jpg</t>
   </si>
   <si>
-    <t>AftenVuelta.jpg</t>
-  </si>
-  <si>
     <t>Aftentour.jpg</t>
   </si>
   <si>
-    <t>Atletik Diamond League.jpg</t>
-  </si>
-  <si>
     <t>Badminton.jpg</t>
   </si>
   <si>
-    <t>Betinia Liga.jpg</t>
-  </si>
-  <si>
     <t>Bundesliga Review of the Midseason.jpg</t>
   </si>
   <si>
@@ -334,9 +1403,6 @@
     <t>Cykling Volta.jpg</t>
   </si>
   <si>
-    <t>Cykling-generic.jpg</t>
-  </si>
-  <si>
     <t>Cykling-generic2.jpg</t>
   </si>
   <si>
@@ -352,9 +1418,6 @@
     <t>Danskerklubben.jpg</t>
   </si>
   <si>
-    <t>EFL Championship Highligts.jpg</t>
-  </si>
-  <si>
     <t>EM i atletik.jpg</t>
   </si>
   <si>
@@ -373,9 +1436,6 @@
     <t>Fodbold Friuli Venezia Giulia Cup - Kampe.jpg</t>
   </si>
   <si>
-    <t>Fodbold.jpg</t>
-  </si>
-  <si>
     <t>Formel 1 Belgien Grand Prix.jpg</t>
   </si>
   <si>
@@ -394,18 +1454,12 @@
     <t>Håndbold  Golden League.jpg</t>
   </si>
   <si>
-    <t>Håndbold Herreligaen.jpg</t>
-  </si>
-  <si>
     <t>Håndbold Kvindeligaen.jpg</t>
   </si>
   <si>
     <t>Højdepunkter fra Dansk Motorsport.jpg</t>
   </si>
   <si>
-    <t>IndyCar.jpg</t>
-  </si>
-  <si>
     <t>Le Mans.jpg</t>
   </si>
   <si>
@@ -433,9 +1487,6 @@
     <t>NFL Gameday.jpg</t>
   </si>
   <si>
-    <t>NFL.jpg</t>
-  </si>
-  <si>
     <t>NFL2.jpg</t>
   </si>
   <si>
@@ -463,15 +1514,9 @@
     <t>Premier League Review.jpg</t>
   </si>
   <si>
-    <t>Premier League.jpg</t>
-  </si>
-  <si>
     <t>Sendeophold.jpg</t>
   </si>
   <si>
-    <t>Serie A.jpg</t>
-  </si>
-  <si>
     <t>Skisport.jpg</t>
   </si>
   <si>
@@ -484,18 +1529,9 @@
     <t>Sport News.jpg</t>
   </si>
   <si>
-    <t>Sporten.jpg</t>
-  </si>
-  <si>
     <t>Spot på Betinia Liga.jpg</t>
   </si>
   <si>
-    <t>Superliga Studiet.jpg</t>
-  </si>
-  <si>
-    <t>Superligatilsynet.jpg</t>
-  </si>
-  <si>
     <t>TV-Udbruddet.jpg</t>
   </si>
   <si>
@@ -505,9 +1541,6 @@
     <t>Tennis ATP 1000.jpg</t>
   </si>
   <si>
-    <t>Tennis ATP 500.jpg</t>
-  </si>
-  <si>
     <t>Tennis Billie-Jean-King-Cup.jpg</t>
   </si>
   <si>
@@ -535,9 +1568,6 @@
     <t>UEFA Super Cup.jpg</t>
   </si>
   <si>
-    <t>VM i MTB.jpg</t>
-  </si>
-  <si>
     <t>VM i dressur.jpg</t>
   </si>
   <si>
@@ -547,9 +1577,6 @@
     <t>Viaplay_Sport_News-generic.jpg</t>
   </si>
   <si>
-    <t>Vuelta a España.jpeg</t>
-  </si>
-  <si>
     <t>WTA-1000.jpg</t>
   </si>
   <si>
@@ -559,18 +1586,12 @@
     <t>WTA-500.jpg</t>
   </si>
   <si>
-    <t>WTA-generic.jpg</t>
-  </si>
-  <si>
     <t>cykling4.jpg</t>
   </si>
   <si>
     <t>tv2sport-generic.jpg</t>
   </si>
   <si>
-    <t>tv3sport-generic.jpg</t>
-  </si>
-  <si>
     <t>Sådan bruger du denne fil</t>
   </si>
   <si>
@@ -580,6 +1601,12 @@
     <t>Angiver hvilken af dine tre kanalgrupper (A/B/C) titlen tilhører.</t>
   </si>
   <si>
+    <t>Kolonne B - Kanaler (alle varianter)</t>
+  </si>
+  <si>
+    <t>Til orientering: ALLE kanal-ID-varianter (adskilt af '; ') hvor denne titel er set. Én titel = ÉN række, uanset hvor mange kanal-varianter (fx 'TV3 Max.dk', 'TV3 MAX HD (D) (T).dk') den optræder på.</t>
+  </si>
+  <si>
     <t>Kolonne D - Nuværende billede</t>
   </si>
   <si>
@@ -613,7 +1640,7 @@
     <t>Kør derefter enrich_epg.py igen, for at få de nye billeder ind i dine XML-filer.</t>
   </si>
   <si>
-    <t>Kør export_sport_review.py igen når som helst - dine tidligere valg BEVARES automatisk (nøgle: gruppe+kanal+titel), kun nye rækker tilføjes. Titler markeret 'Ignorer...' i Note udelades permanent fra fremtidige eksporter (for alle kanal-varianter).</t>
+    <t>Kør export_sport_review.py igen når som helst - dine tidligere valg BEVARES automatisk (nøgle: gruppe+titel), kun nye titler tilføjes. Titler markeret 'Ignorer...' i Note udelades permanent fra fremtidige eksporter.</t>
   </si>
   <si>
     <t>Der laves automatisk en sikkerhedskopi (sport_artwork_review.BACKUP.xlsx) FØR filen overskrives, hver gang du kører export_sport_review.py.</t>
@@ -984,11 +2011,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G338"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
@@ -1032,19 +2059,25 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1052,13 +2085,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1066,13 +2102,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1080,13 +2119,16 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1094,13 +2136,16 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1108,19 +2153,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1128,19 +2170,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
       <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1148,19 +2187,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
       <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1168,19 +2204,16 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1188,19 +2221,16 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1208,19 +2238,16 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1228,19 +2255,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1248,19 +2272,16 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
         <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" t="s">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1271,119 +2292,101 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
         <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
         <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
       <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
       <c r="D20" t="s">
         <v>10</v>
       </c>
-      <c r="E20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
       </c>
-      <c r="E21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1391,32 +2394,38 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -1424,960 +2433,5629 @@
       <c r="D24" t="s">
         <v>10</v>
       </c>
-      <c r="E24" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
       </c>
-      <c r="E25" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
       </c>
-      <c r="E26" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
       </c>
-      <c r="E27" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" t="s">
+        <v>71</v>
+      </c>
+      <c r="D47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>51</v>
+      </c>
+      <c r="B50" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" t="s">
+        <v>78</v>
+      </c>
+      <c r="D54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>51</v>
+      </c>
+      <c r="B55" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>51</v>
+      </c>
+      <c r="B56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57" t="s">
+        <v>81</v>
+      </c>
+      <c r="C57" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>51</v>
+      </c>
+      <c r="B59" t="s">
+        <v>52</v>
+      </c>
+      <c r="C59" t="s">
+        <v>84</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>51</v>
+      </c>
+      <c r="B60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" t="s">
+        <v>59</v>
+      </c>
+      <c r="C61" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>51</v>
+      </c>
+      <c r="B62" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>51</v>
+      </c>
+      <c r="B63" t="s">
+        <v>59</v>
+      </c>
+      <c r="C63" t="s">
+        <v>89</v>
+      </c>
+      <c r="D63" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>51</v>
+      </c>
+      <c r="B64" t="s">
+        <v>59</v>
+      </c>
+      <c r="C64" t="s">
+        <v>90</v>
+      </c>
+      <c r="D64" t="s">
+        <v>10</v>
+      </c>
+      <c r="G64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>51</v>
+      </c>
+      <c r="B65" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" t="s">
+        <v>91</v>
+      </c>
+      <c r="D65" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>51</v>
+      </c>
+      <c r="B66" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>51</v>
+      </c>
+      <c r="B67" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" t="s">
+        <v>93</v>
+      </c>
+      <c r="D67" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>51</v>
+      </c>
+      <c r="B68" t="s">
+        <v>52</v>
+      </c>
+      <c r="C68" t="s">
+        <v>94</v>
+      </c>
+      <c r="D68" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>51</v>
+      </c>
+      <c r="B69" t="s">
+        <v>81</v>
+      </c>
+      <c r="C69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D69" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>51</v>
+      </c>
+      <c r="B70" t="s">
+        <v>59</v>
+      </c>
+      <c r="C70" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>51</v>
+      </c>
+      <c r="B71" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>51</v>
+      </c>
+      <c r="B72" t="s">
+        <v>56</v>
+      </c>
+      <c r="C72" t="s">
+        <v>98</v>
+      </c>
+      <c r="D72" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>51</v>
+      </c>
+      <c r="B73" t="s">
+        <v>54</v>
+      </c>
+      <c r="C73" t="s">
+        <v>99</v>
+      </c>
+      <c r="D73" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>51</v>
+      </c>
+      <c r="B74" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>51</v>
+      </c>
+      <c r="B75" t="s">
+        <v>69</v>
+      </c>
+      <c r="C75" t="s">
+        <v>101</v>
+      </c>
+      <c r="D75" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>51</v>
+      </c>
+      <c r="B76" t="s">
+        <v>69</v>
+      </c>
+      <c r="C76" t="s">
+        <v>102</v>
+      </c>
+      <c r="D76" t="s">
+        <v>10</v>
+      </c>
+      <c r="G76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>51</v>
+      </c>
+      <c r="B77" t="s">
+        <v>59</v>
+      </c>
+      <c r="C77" t="s">
+        <v>103</v>
+      </c>
+      <c r="D77" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>51</v>
+      </c>
+      <c r="B78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C78" t="s">
+        <v>104</v>
+      </c>
+      <c r="D78" t="s">
+        <v>10</v>
+      </c>
+      <c r="G78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>51</v>
+      </c>
+      <c r="B79" t="s">
+        <v>61</v>
+      </c>
+      <c r="C79" t="s">
+        <v>105</v>
+      </c>
+      <c r="D79" t="s">
+        <v>10</v>
+      </c>
+      <c r="G79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>51</v>
+      </c>
+      <c r="B80" t="s">
+        <v>63</v>
+      </c>
+      <c r="C80" t="s">
+        <v>106</v>
+      </c>
+      <c r="D80" t="s">
+        <v>10</v>
+      </c>
+      <c r="G80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>51</v>
+      </c>
+      <c r="B81" t="s">
+        <v>61</v>
+      </c>
+      <c r="C81" t="s">
+        <v>107</v>
+      </c>
+      <c r="D81" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>51</v>
+      </c>
+      <c r="B82" t="s">
+        <v>63</v>
+      </c>
+      <c r="C82" t="s">
+        <v>108</v>
+      </c>
+      <c r="D82" t="s">
+        <v>10</v>
+      </c>
+      <c r="G82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>51</v>
+      </c>
+      <c r="B83" t="s">
+        <v>63</v>
+      </c>
+      <c r="C83" t="s">
+        <v>109</v>
+      </c>
+      <c r="D83" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>51</v>
+      </c>
+      <c r="B84" t="s">
+        <v>61</v>
+      </c>
+      <c r="C84" t="s">
+        <v>110</v>
+      </c>
+      <c r="D84" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>51</v>
+      </c>
+      <c r="B85" t="s">
+        <v>63</v>
+      </c>
+      <c r="C85" t="s">
+        <v>111</v>
+      </c>
+      <c r="D85" t="s">
+        <v>10</v>
+      </c>
+      <c r="G85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>51</v>
+      </c>
+      <c r="B86" t="s">
+        <v>63</v>
+      </c>
+      <c r="C86" t="s">
+        <v>112</v>
+      </c>
+      <c r="D86" t="s">
+        <v>10</v>
+      </c>
+      <c r="G86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>51</v>
+      </c>
+      <c r="B87" t="s">
+        <v>54</v>
+      </c>
+      <c r="C87" t="s">
+        <v>113</v>
+      </c>
+      <c r="D87" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>51</v>
+      </c>
+      <c r="B88" t="s">
+        <v>69</v>
+      </c>
+      <c r="C88" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>51</v>
+      </c>
+      <c r="B89" t="s">
+        <v>115</v>
+      </c>
+      <c r="C89" t="s">
+        <v>116</v>
+      </c>
+      <c r="D89" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>51</v>
+      </c>
+      <c r="B90" t="s">
+        <v>52</v>
+      </c>
+      <c r="C90" t="s">
+        <v>117</v>
+      </c>
+      <c r="D90" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>51</v>
+      </c>
+      <c r="B91" t="s">
+        <v>118</v>
+      </c>
+      <c r="C91" t="s">
+        <v>119</v>
+      </c>
+      <c r="D91" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>51</v>
+      </c>
+      <c r="B92" t="s">
+        <v>81</v>
+      </c>
+      <c r="C92" t="s">
+        <v>120</v>
+      </c>
+      <c r="D92" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>51</v>
+      </c>
+      <c r="B93" t="s">
+        <v>81</v>
+      </c>
+      <c r="C93" t="s">
+        <v>121</v>
+      </c>
+      <c r="D93" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>51</v>
+      </c>
+      <c r="B94" t="s">
+        <v>54</v>
+      </c>
+      <c r="C94" t="s">
+        <v>122</v>
+      </c>
+      <c r="D94" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>51</v>
+      </c>
+      <c r="B95" t="s">
+        <v>69</v>
+      </c>
+      <c r="C95" t="s">
+        <v>123</v>
+      </c>
+      <c r="D95" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>51</v>
+      </c>
+      <c r="B96" t="s">
+        <v>56</v>
+      </c>
+      <c r="C96" t="s">
+        <v>124</v>
+      </c>
+      <c r="D96" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>51</v>
+      </c>
+      <c r="B97" t="s">
+        <v>54</v>
+      </c>
+      <c r="C97" t="s">
+        <v>125</v>
+      </c>
+      <c r="D97" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>51</v>
+      </c>
+      <c r="B98" t="s">
+        <v>56</v>
+      </c>
+      <c r="C98" t="s">
+        <v>126</v>
+      </c>
+      <c r="D98" t="s">
+        <v>10</v>
+      </c>
+      <c r="G98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>51</v>
+      </c>
+      <c r="B99" t="s">
+        <v>54</v>
+      </c>
+      <c r="C99" t="s">
+        <v>127</v>
+      </c>
+      <c r="D99" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>51</v>
+      </c>
+      <c r="B100" t="s">
+        <v>69</v>
+      </c>
+      <c r="C100" t="s">
+        <v>128</v>
+      </c>
+      <c r="D100" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>51</v>
+      </c>
+      <c r="B101" t="s">
+        <v>56</v>
+      </c>
+      <c r="C101" t="s">
+        <v>129</v>
+      </c>
+      <c r="D101" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>51</v>
+      </c>
+      <c r="B102" t="s">
+        <v>61</v>
+      </c>
+      <c r="C102" t="s">
+        <v>130</v>
+      </c>
+      <c r="D102" t="s">
+        <v>10</v>
+      </c>
+      <c r="G102" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>51</v>
+      </c>
+      <c r="B103" t="s">
+        <v>63</v>
+      </c>
+      <c r="C103" t="s">
+        <v>131</v>
+      </c>
+      <c r="D103" t="s">
+        <v>10</v>
+      </c>
+      <c r="G103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>51</v>
+      </c>
+      <c r="B104" t="s">
+        <v>59</v>
+      </c>
+      <c r="C104" t="s">
+        <v>132</v>
+      </c>
+      <c r="D104" t="s">
+        <v>10</v>
+      </c>
+      <c r="G104" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>51</v>
+      </c>
+      <c r="B105" t="s">
+        <v>61</v>
+      </c>
+      <c r="C105" t="s">
+        <v>133</v>
+      </c>
+      <c r="D105" t="s">
+        <v>10</v>
+      </c>
+      <c r="G105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>51</v>
+      </c>
+      <c r="B106" t="s">
+        <v>59</v>
+      </c>
+      <c r="C106" t="s">
+        <v>134</v>
+      </c>
+      <c r="D106" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>51</v>
+      </c>
+      <c r="B107" t="s">
+        <v>63</v>
+      </c>
+      <c r="C107" t="s">
+        <v>135</v>
+      </c>
+      <c r="D107" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>51</v>
+      </c>
+      <c r="B108" t="s">
+        <v>61</v>
+      </c>
+      <c r="C108" t="s">
+        <v>136</v>
+      </c>
+      <c r="D108" t="s">
+        <v>10</v>
+      </c>
+      <c r="G108" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>51</v>
+      </c>
+      <c r="B109" t="s">
+        <v>63</v>
+      </c>
+      <c r="C109" t="s">
+        <v>137</v>
+      </c>
+      <c r="D109" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>51</v>
+      </c>
+      <c r="B110" t="s">
+        <v>54</v>
+      </c>
+      <c r="C110" t="s">
+        <v>138</v>
+      </c>
+      <c r="D110" t="s">
+        <v>10</v>
+      </c>
+      <c r="G110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>51</v>
+      </c>
+      <c r="B111" t="s">
+        <v>115</v>
+      </c>
+      <c r="C111" t="s">
+        <v>139</v>
+      </c>
+      <c r="D111" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>51</v>
+      </c>
+      <c r="B112" t="s">
+        <v>69</v>
+      </c>
+      <c r="C112" t="s">
+        <v>140</v>
+      </c>
+      <c r="D112" t="s">
+        <v>10</v>
+      </c>
+      <c r="G112" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>51</v>
+      </c>
+      <c r="B113" t="s">
+        <v>61</v>
+      </c>
+      <c r="C113" t="s">
+        <v>141</v>
+      </c>
+      <c r="D113" t="s">
+        <v>10</v>
+      </c>
+      <c r="G113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>51</v>
+      </c>
+      <c r="B114" t="s">
+        <v>63</v>
+      </c>
+      <c r="C114" t="s">
+        <v>142</v>
+      </c>
+      <c r="D114" t="s">
+        <v>10</v>
+      </c>
+      <c r="G114" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>51</v>
+      </c>
+      <c r="B115" t="s">
+        <v>81</v>
+      </c>
+      <c r="C115" t="s">
+        <v>143</v>
+      </c>
+      <c r="D115" t="s">
+        <v>10</v>
+      </c>
+      <c r="G115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>51</v>
+      </c>
+      <c r="B116" t="s">
+        <v>144</v>
+      </c>
+      <c r="C116" t="s">
         <v>145</v>
       </c>
-      <c r="F28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="D116" t="s">
+        <v>10</v>
+      </c>
+      <c r="G116" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>51</v>
+      </c>
+      <c r="B117" t="s">
+        <v>118</v>
+      </c>
+      <c r="C117" t="s">
+        <v>146</v>
+      </c>
+      <c r="D117" t="s">
+        <v>10</v>
+      </c>
+      <c r="G117" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>51</v>
+      </c>
+      <c r="B118" t="s">
+        <v>54</v>
+      </c>
+      <c r="C118" t="s">
+        <v>147</v>
+      </c>
+      <c r="D118" t="s">
+        <v>10</v>
+      </c>
+      <c r="G118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>51</v>
+      </c>
+      <c r="B119" t="s">
+        <v>56</v>
+      </c>
+      <c r="C119" t="s">
+        <v>148</v>
+      </c>
+      <c r="D119" t="s">
+        <v>10</v>
+      </c>
+      <c r="G119" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>51</v>
+      </c>
+      <c r="B120" t="s">
+        <v>54</v>
+      </c>
+      <c r="C120" t="s">
+        <v>149</v>
+      </c>
+      <c r="D120" t="s">
+        <v>10</v>
+      </c>
+      <c r="G120" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>51</v>
+      </c>
+      <c r="B121" t="s">
+        <v>69</v>
+      </c>
+      <c r="C121" t="s">
+        <v>150</v>
+      </c>
+      <c r="D121" t="s">
+        <v>10</v>
+      </c>
+      <c r="G121" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>51</v>
+      </c>
+      <c r="B122" t="s">
+        <v>56</v>
+      </c>
+      <c r="C122" t="s">
+        <v>151</v>
+      </c>
+      <c r="D122" t="s">
+        <v>10</v>
+      </c>
+      <c r="G122" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>51</v>
+      </c>
+      <c r="B123" t="s">
+        <v>52</v>
+      </c>
+      <c r="C123" t="s">
+        <v>152</v>
+      </c>
+      <c r="D123" t="s">
+        <v>10</v>
+      </c>
+      <c r="G123" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>51</v>
+      </c>
+      <c r="B124" t="s">
+        <v>54</v>
+      </c>
+      <c r="C124" t="s">
+        <v>153</v>
+      </c>
+      <c r="D124" t="s">
+        <v>10</v>
+      </c>
+      <c r="G124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>51</v>
+      </c>
+      <c r="B125" t="s">
+        <v>56</v>
+      </c>
+      <c r="C125" t="s">
+        <v>154</v>
+      </c>
+      <c r="D125" t="s">
+        <v>10</v>
+      </c>
+      <c r="G125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>51</v>
+      </c>
+      <c r="B126" t="s">
+        <v>56</v>
+      </c>
+      <c r="C126" t="s">
+        <v>155</v>
+      </c>
+      <c r="D126" t="s">
+        <v>10</v>
+      </c>
+      <c r="G126" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>51</v>
+      </c>
+      <c r="B127" t="s">
+        <v>54</v>
+      </c>
+      <c r="C127" t="s">
+        <v>156</v>
+      </c>
+      <c r="D127" t="s">
+        <v>10</v>
+      </c>
+      <c r="G127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>51</v>
+      </c>
+      <c r="B128" t="s">
+        <v>56</v>
+      </c>
+      <c r="C128" t="s">
+        <v>157</v>
+      </c>
+      <c r="D128" t="s">
+        <v>10</v>
+      </c>
+      <c r="G128" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>51</v>
+      </c>
+      <c r="B129" t="s">
+        <v>56</v>
+      </c>
+      <c r="C129" t="s">
+        <v>158</v>
+      </c>
+      <c r="D129" t="s">
+        <v>10</v>
+      </c>
+      <c r="G129" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>51</v>
+      </c>
+      <c r="B130" t="s">
+        <v>56</v>
+      </c>
+      <c r="C130" t="s">
+        <v>159</v>
+      </c>
+      <c r="D130" t="s">
+        <v>10</v>
+      </c>
+      <c r="G130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>51</v>
+      </c>
+      <c r="B131" t="s">
+        <v>59</v>
+      </c>
+      <c r="C131" t="s">
+        <v>160</v>
+      </c>
+      <c r="D131" t="s">
+        <v>10</v>
+      </c>
+      <c r="G131" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>51</v>
+      </c>
+      <c r="B132" t="s">
+        <v>59</v>
+      </c>
+      <c r="C132" t="s">
+        <v>161</v>
+      </c>
+      <c r="D132" t="s">
+        <v>10</v>
+      </c>
+      <c r="G132" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>51</v>
+      </c>
+      <c r="B133" t="s">
+        <v>63</v>
+      </c>
+      <c r="C133" t="s">
+        <v>162</v>
+      </c>
+      <c r="D133" t="s">
+        <v>10</v>
+      </c>
+      <c r="G133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>51</v>
+      </c>
+      <c r="B134" t="s">
+        <v>54</v>
+      </c>
+      <c r="C134" t="s">
+        <v>163</v>
+      </c>
+      <c r="D134" t="s">
+        <v>10</v>
+      </c>
+      <c r="G134" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>51</v>
+      </c>
+      <c r="B135" t="s">
+        <v>115</v>
+      </c>
+      <c r="C135" t="s">
+        <v>164</v>
+      </c>
+      <c r="D135" t="s">
+        <v>10</v>
+      </c>
+      <c r="G135" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>51</v>
+      </c>
+      <c r="B136" t="s">
+        <v>69</v>
+      </c>
+      <c r="C136" t="s">
+        <v>165</v>
+      </c>
+      <c r="D136" t="s">
+        <v>10</v>
+      </c>
+      <c r="G136" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>51</v>
+      </c>
+      <c r="B137" t="s">
+        <v>69</v>
+      </c>
+      <c r="C137" t="s">
+        <v>166</v>
+      </c>
+      <c r="D137" t="s">
+        <v>10</v>
+      </c>
+      <c r="G137" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>51</v>
+      </c>
+      <c r="B138" t="s">
+        <v>61</v>
+      </c>
+      <c r="C138" t="s">
+        <v>167</v>
+      </c>
+      <c r="D138" t="s">
+        <v>10</v>
+      </c>
+      <c r="G138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>51</v>
+      </c>
+      <c r="B139" t="s">
+        <v>63</v>
+      </c>
+      <c r="C139" t="s">
+        <v>168</v>
+      </c>
+      <c r="D139" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>51</v>
+      </c>
+      <c r="B140" t="s">
+        <v>59</v>
+      </c>
+      <c r="C140" t="s">
+        <v>169</v>
+      </c>
+      <c r="D140" t="s">
+        <v>10</v>
+      </c>
+      <c r="G140" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>51</v>
+      </c>
+      <c r="B141" t="s">
+        <v>54</v>
+      </c>
+      <c r="C141" t="s">
+        <v>170</v>
+      </c>
+      <c r="D141" t="s">
+        <v>10</v>
+      </c>
+      <c r="G141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>51</v>
+      </c>
+      <c r="B142" t="s">
+        <v>56</v>
+      </c>
+      <c r="C142" t="s">
+        <v>171</v>
+      </c>
+      <c r="D142" t="s">
+        <v>10</v>
+      </c>
+      <c r="G142" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>51</v>
+      </c>
+      <c r="B143" t="s">
+        <v>81</v>
+      </c>
+      <c r="C143" t="s">
+        <v>172</v>
+      </c>
+      <c r="D143" t="s">
+        <v>10</v>
+      </c>
+      <c r="G143" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>51</v>
+      </c>
+      <c r="B144" t="s">
+        <v>81</v>
+      </c>
+      <c r="C144" t="s">
+        <v>173</v>
+      </c>
+      <c r="D144" t="s">
+        <v>10</v>
+      </c>
+      <c r="G144" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>51</v>
+      </c>
+      <c r="B145" t="s">
+        <v>174</v>
+      </c>
+      <c r="C145" t="s">
+        <v>175</v>
+      </c>
+      <c r="D145" t="s">
+        <v>10</v>
+      </c>
+      <c r="G145" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>51</v>
+      </c>
+      <c r="B146" t="s">
+        <v>63</v>
+      </c>
+      <c r="C146" t="s">
+        <v>176</v>
+      </c>
+      <c r="D146" t="s">
+        <v>10</v>
+      </c>
+      <c r="G146" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>51</v>
+      </c>
+      <c r="B147" t="s">
+        <v>54</v>
+      </c>
+      <c r="C147" t="s">
+        <v>177</v>
+      </c>
+      <c r="D147" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>51</v>
+      </c>
+      <c r="B148" t="s">
+        <v>69</v>
+      </c>
+      <c r="C148" t="s">
+        <v>178</v>
+      </c>
+      <c r="D148" t="s">
+        <v>10</v>
+      </c>
+      <c r="G148" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>51</v>
+      </c>
+      <c r="B149" t="s">
+        <v>115</v>
+      </c>
+      <c r="C149" t="s">
+        <v>179</v>
+      </c>
+      <c r="D149" t="s">
+        <v>10</v>
+      </c>
+      <c r="G149" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>51</v>
+      </c>
+      <c r="B150" t="s">
+        <v>54</v>
+      </c>
+      <c r="C150" t="s">
+        <v>180</v>
+      </c>
+      <c r="D150" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>51</v>
+      </c>
+      <c r="B151" t="s">
+        <v>56</v>
+      </c>
+      <c r="C151" t="s">
+        <v>181</v>
+      </c>
+      <c r="D151" t="s">
+        <v>10</v>
+      </c>
+      <c r="G151" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>51</v>
+      </c>
+      <c r="B152" t="s">
+        <v>56</v>
+      </c>
+      <c r="C152" t="s">
+        <v>182</v>
+      </c>
+      <c r="D152" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>51</v>
+      </c>
+      <c r="B153" t="s">
+        <v>81</v>
+      </c>
+      <c r="C153" t="s">
+        <v>183</v>
+      </c>
+      <c r="D153" t="s">
+        <v>10</v>
+      </c>
+      <c r="G153" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>51</v>
+      </c>
+      <c r="B154" t="s">
+        <v>52</v>
+      </c>
+      <c r="C154" t="s">
+        <v>184</v>
+      </c>
+      <c r="D154" t="s">
+        <v>10</v>
+      </c>
+      <c r="G154" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>51</v>
+      </c>
+      <c r="B155" t="s">
+        <v>54</v>
+      </c>
+      <c r="C155" t="s">
+        <v>185</v>
+      </c>
+      <c r="D155" t="s">
+        <v>10</v>
+      </c>
+      <c r="G155" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>51</v>
+      </c>
+      <c r="B156" t="s">
+        <v>56</v>
+      </c>
+      <c r="C156" t="s">
+        <v>186</v>
+      </c>
+      <c r="D156" t="s">
+        <v>10</v>
+      </c>
+      <c r="G156" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>51</v>
+      </c>
+      <c r="B157" t="s">
+        <v>61</v>
+      </c>
+      <c r="C157" t="s">
+        <v>187</v>
+      </c>
+      <c r="D157" t="s">
+        <v>10</v>
+      </c>
+      <c r="G157" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>51</v>
+      </c>
+      <c r="B158" t="s">
+        <v>63</v>
+      </c>
+      <c r="C158" t="s">
+        <v>188</v>
+      </c>
+      <c r="D158" t="s">
+        <v>10</v>
+      </c>
+      <c r="G158" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>51</v>
+      </c>
+      <c r="B159" t="s">
+        <v>59</v>
+      </c>
+      <c r="C159" t="s">
+        <v>189</v>
+      </c>
+      <c r="D159" t="s">
+        <v>10</v>
+      </c>
+      <c r="G159" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>51</v>
+      </c>
+      <c r="B160" t="s">
+        <v>61</v>
+      </c>
+      <c r="C160" t="s">
+        <v>190</v>
+      </c>
+      <c r="D160" t="s">
+        <v>10</v>
+      </c>
+      <c r="G160" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>51</v>
+      </c>
+      <c r="B161" t="s">
+        <v>54</v>
+      </c>
+      <c r="C161" t="s">
+        <v>191</v>
+      </c>
+      <c r="D161" t="s">
+        <v>10</v>
+      </c>
+      <c r="G161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>51</v>
+      </c>
+      <c r="B162" t="s">
+        <v>56</v>
+      </c>
+      <c r="C162" t="s">
+        <v>192</v>
+      </c>
+      <c r="D162" t="s">
+        <v>10</v>
+      </c>
+      <c r="G162" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>51</v>
+      </c>
+      <c r="B163" t="s">
+        <v>61</v>
+      </c>
+      <c r="C163" t="s">
+        <v>193</v>
+      </c>
+      <c r="D163" t="s">
+        <v>10</v>
+      </c>
+      <c r="G163" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>51</v>
+      </c>
+      <c r="B164" t="s">
+        <v>118</v>
+      </c>
+      <c r="C164" t="s">
+        <v>194</v>
+      </c>
+      <c r="D164" t="s">
+        <v>10</v>
+      </c>
+      <c r="G164" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>51</v>
+      </c>
+      <c r="B165" t="s">
+        <v>59</v>
+      </c>
+      <c r="C165" t="s">
+        <v>195</v>
+      </c>
+      <c r="D165" t="s">
+        <v>10</v>
+      </c>
+      <c r="G165" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>51</v>
+      </c>
+      <c r="B166" t="s">
+        <v>63</v>
+      </c>
+      <c r="C166" t="s">
+        <v>196</v>
+      </c>
+      <c r="D166" t="s">
+        <v>10</v>
+      </c>
+      <c r="G166" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>51</v>
+      </c>
+      <c r="B167" t="s">
+        <v>52</v>
+      </c>
+      <c r="C167" t="s">
+        <v>197</v>
+      </c>
+      <c r="D167" t="s">
+        <v>10</v>
+      </c>
+      <c r="G167" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>51</v>
+      </c>
+      <c r="B168" t="s">
+        <v>61</v>
+      </c>
+      <c r="C168" t="s">
+        <v>198</v>
+      </c>
+      <c r="D168" t="s">
+        <v>10</v>
+      </c>
+      <c r="G168" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>51</v>
+      </c>
+      <c r="B169" t="s">
+        <v>59</v>
+      </c>
+      <c r="C169" t="s">
+        <v>199</v>
+      </c>
+      <c r="D169" t="s">
+        <v>10</v>
+      </c>
+      <c r="G169" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>51</v>
+      </c>
+      <c r="B170" t="s">
+        <v>63</v>
+      </c>
+      <c r="C170" t="s">
+        <v>200</v>
+      </c>
+      <c r="D170" t="s">
+        <v>10</v>
+      </c>
+      <c r="G170" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>51</v>
+      </c>
+      <c r="B171" t="s">
+        <v>201</v>
+      </c>
+      <c r="C171" t="s">
+        <v>202</v>
+      </c>
+      <c r="D171" t="s">
+        <v>10</v>
+      </c>
+      <c r="G171" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>51</v>
+      </c>
+      <c r="B172" t="s">
+        <v>118</v>
+      </c>
+      <c r="C172" t="s">
+        <v>203</v>
+      </c>
+      <c r="D172" t="s">
+        <v>10</v>
+      </c>
+      <c r="G172" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>51</v>
+      </c>
+      <c r="B173" t="s">
+        <v>118</v>
+      </c>
+      <c r="C173" t="s">
+        <v>204</v>
+      </c>
+      <c r="D173" t="s">
+        <v>10</v>
+      </c>
+      <c r="G173" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>51</v>
+      </c>
+      <c r="B174" t="s">
+        <v>54</v>
+      </c>
+      <c r="C174" t="s">
+        <v>205</v>
+      </c>
+      <c r="D174" t="s">
+        <v>10</v>
+      </c>
+      <c r="G174" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>51</v>
+      </c>
+      <c r="B175" t="s">
+        <v>69</v>
+      </c>
+      <c r="C175" t="s">
+        <v>206</v>
+      </c>
+      <c r="D175" t="s">
+        <v>10</v>
+      </c>
+      <c r="G175" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>51</v>
+      </c>
+      <c r="B176" t="s">
+        <v>61</v>
+      </c>
+      <c r="C176" t="s">
+        <v>207</v>
+      </c>
+      <c r="D176" t="s">
+        <v>10</v>
+      </c>
+      <c r="G176" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>51</v>
+      </c>
+      <c r="B177" t="s">
+        <v>118</v>
+      </c>
+      <c r="C177" t="s">
+        <v>208</v>
+      </c>
+      <c r="D177" t="s">
+        <v>10</v>
+      </c>
+      <c r="G177" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>51</v>
+      </c>
+      <c r="B178" t="s">
+        <v>52</v>
+      </c>
+      <c r="C178" t="s">
+        <v>209</v>
+      </c>
+      <c r="D178" t="s">
+        <v>10</v>
+      </c>
+      <c r="G178" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>51</v>
+      </c>
+      <c r="B179" t="s">
+        <v>69</v>
+      </c>
+      <c r="C179" t="s">
+        <v>210</v>
+      </c>
+      <c r="D179" t="s">
+        <v>10</v>
+      </c>
+      <c r="G179" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>51</v>
+      </c>
+      <c r="B180" t="s">
+        <v>59</v>
+      </c>
+      <c r="C180" t="s">
+        <v>211</v>
+      </c>
+      <c r="D180" t="s">
+        <v>10</v>
+      </c>
+      <c r="G180" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>51</v>
+      </c>
+      <c r="B181" t="s">
+        <v>63</v>
+      </c>
+      <c r="C181" t="s">
+        <v>212</v>
+      </c>
+      <c r="D181" t="s">
+        <v>10</v>
+      </c>
+      <c r="G181" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>51</v>
+      </c>
+      <c r="B182" t="s">
+        <v>61</v>
+      </c>
+      <c r="C182" t="s">
+        <v>213</v>
+      </c>
+      <c r="D182" t="s">
+        <v>10</v>
+      </c>
+      <c r="G182" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>51</v>
+      </c>
+      <c r="B183" t="s">
+        <v>63</v>
+      </c>
+      <c r="C183" t="s">
+        <v>214</v>
+      </c>
+      <c r="D183" t="s">
+        <v>10</v>
+      </c>
+      <c r="G183" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>51</v>
+      </c>
+      <c r="B184" t="s">
+        <v>54</v>
+      </c>
+      <c r="C184" t="s">
+        <v>215</v>
+      </c>
+      <c r="D184" t="s">
+        <v>10</v>
+      </c>
+      <c r="G184" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>51</v>
+      </c>
+      <c r="B185" t="s">
+        <v>56</v>
+      </c>
+      <c r="C185" t="s">
+        <v>216</v>
+      </c>
+      <c r="D185" t="s">
+        <v>10</v>
+      </c>
+      <c r="G185" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>51</v>
+      </c>
+      <c r="B186" t="s">
+        <v>69</v>
+      </c>
+      <c r="C186" t="s">
+        <v>217</v>
+      </c>
+      <c r="D186" t="s">
+        <v>10</v>
+      </c>
+      <c r="G186" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>51</v>
+      </c>
+      <c r="B187" t="s">
+        <v>54</v>
+      </c>
+      <c r="C187" t="s">
+        <v>218</v>
+      </c>
+      <c r="D187" t="s">
+        <v>10</v>
+      </c>
+      <c r="G187" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>51</v>
+      </c>
+      <c r="B188" t="s">
+        <v>56</v>
+      </c>
+      <c r="C188" t="s">
+        <v>219</v>
+      </c>
+      <c r="D188" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>51</v>
+      </c>
+      <c r="B189" t="s">
+        <v>61</v>
+      </c>
+      <c r="C189" t="s">
+        <v>220</v>
+      </c>
+      <c r="D189" t="s">
+        <v>10</v>
+      </c>
+      <c r="G189" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>51</v>
+      </c>
+      <c r="B190" t="s">
+        <v>63</v>
+      </c>
+      <c r="C190" t="s">
+        <v>221</v>
+      </c>
+      <c r="D190" t="s">
+        <v>10</v>
+      </c>
+      <c r="G190" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>51</v>
+      </c>
+      <c r="B191" t="s">
+        <v>54</v>
+      </c>
+      <c r="C191" t="s">
+        <v>222</v>
+      </c>
+      <c r="D191" t="s">
+        <v>10</v>
+      </c>
+      <c r="G191" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>51</v>
+      </c>
+      <c r="B192" t="s">
+        <v>56</v>
+      </c>
+      <c r="C192" t="s">
+        <v>223</v>
+      </c>
+      <c r="D192" t="s">
+        <v>10</v>
+      </c>
+      <c r="G192" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>51</v>
+      </c>
+      <c r="B193" t="s">
+        <v>54</v>
+      </c>
+      <c r="C193" t="s">
+        <v>224</v>
+      </c>
+      <c r="D193" t="s">
+        <v>10</v>
+      </c>
+      <c r="G193" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>51</v>
+      </c>
+      <c r="B194" t="s">
+        <v>69</v>
+      </c>
+      <c r="C194" t="s">
+        <v>225</v>
+      </c>
+      <c r="D194" t="s">
+        <v>10</v>
+      </c>
+      <c r="G194" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>51</v>
+      </c>
+      <c r="B195" t="s">
+        <v>56</v>
+      </c>
+      <c r="C195" t="s">
+        <v>226</v>
+      </c>
+      <c r="D195" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>51</v>
+      </c>
+      <c r="B196" t="s">
+        <v>81</v>
+      </c>
+      <c r="C196" t="s">
+        <v>227</v>
+      </c>
+      <c r="D196" t="s">
+        <v>10</v>
+      </c>
+      <c r="G196" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>51</v>
+      </c>
+      <c r="B197" t="s">
+        <v>118</v>
+      </c>
+      <c r="C197" t="s">
+        <v>228</v>
+      </c>
+      <c r="D197" t="s">
+        <v>10</v>
+      </c>
+      <c r="G197" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>51</v>
+      </c>
+      <c r="B198" t="s">
+        <v>81</v>
+      </c>
+      <c r="C198" t="s">
+        <v>229</v>
+      </c>
+      <c r="D198" t="s">
+        <v>10</v>
+      </c>
+      <c r="G198" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>51</v>
+      </c>
+      <c r="B199" t="s">
+        <v>81</v>
+      </c>
+      <c r="C199" t="s">
+        <v>230</v>
+      </c>
+      <c r="D199" t="s">
+        <v>10</v>
+      </c>
+      <c r="G199" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>51</v>
+      </c>
+      <c r="B200" t="s">
+        <v>52</v>
+      </c>
+      <c r="C200" t="s">
+        <v>231</v>
+      </c>
+      <c r="D200" t="s">
+        <v>10</v>
+      </c>
+      <c r="G200" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>51</v>
+      </c>
+      <c r="B201" t="s">
+        <v>232</v>
+      </c>
+      <c r="C201" t="s">
+        <v>233</v>
+      </c>
+      <c r="D201" t="s">
+        <v>10</v>
+      </c>
+      <c r="G201" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>51</v>
+      </c>
+      <c r="B202" t="s">
+        <v>52</v>
+      </c>
+      <c r="C202" t="s">
+        <v>234</v>
+      </c>
+      <c r="D202" t="s">
+        <v>10</v>
+      </c>
+      <c r="G202" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>51</v>
+      </c>
+      <c r="B203" t="s">
+        <v>54</v>
+      </c>
+      <c r="C203" t="s">
+        <v>235</v>
+      </c>
+      <c r="D203" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>51</v>
+      </c>
+      <c r="B204" t="s">
+        <v>56</v>
+      </c>
+      <c r="C204" t="s">
+        <v>236</v>
+      </c>
+      <c r="D204" t="s">
+        <v>10</v>
+      </c>
+      <c r="G204" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>51</v>
+      </c>
+      <c r="B205" t="s">
+        <v>54</v>
+      </c>
+      <c r="C205" t="s">
+        <v>237</v>
+      </c>
+      <c r="D205" t="s">
+        <v>10</v>
+      </c>
+      <c r="G205" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>51</v>
+      </c>
+      <c r="B206" t="s">
+        <v>56</v>
+      </c>
+      <c r="C206" t="s">
+        <v>238</v>
+      </c>
+      <c r="D206" t="s">
+        <v>10</v>
+      </c>
+      <c r="G206" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>51</v>
+      </c>
+      <c r="B207" t="s">
+        <v>56</v>
+      </c>
+      <c r="C207" t="s">
+        <v>239</v>
+      </c>
+      <c r="D207" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>51</v>
+      </c>
+      <c r="B208" t="s">
+        <v>69</v>
+      </c>
+      <c r="C208" t="s">
+        <v>240</v>
+      </c>
+      <c r="D208" t="s">
+        <v>10</v>
+      </c>
+      <c r="G208" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>51</v>
+      </c>
+      <c r="B209" t="s">
+        <v>56</v>
+      </c>
+      <c r="C209" t="s">
+        <v>241</v>
+      </c>
+      <c r="D209" t="s">
+        <v>10</v>
+      </c>
+      <c r="G209" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>51</v>
+      </c>
+      <c r="B210" t="s">
+        <v>54</v>
+      </c>
+      <c r="C210" t="s">
+        <v>242</v>
+      </c>
+      <c r="D210" t="s">
+        <v>10</v>
+      </c>
+      <c r="G210" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>51</v>
+      </c>
+      <c r="B211" t="s">
+        <v>54</v>
+      </c>
+      <c r="C211" t="s">
+        <v>243</v>
+      </c>
+      <c r="D211" t="s">
+        <v>10</v>
+      </c>
+      <c r="G211" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>51</v>
+      </c>
+      <c r="B212" t="s">
+        <v>56</v>
+      </c>
+      <c r="C212" t="s">
+        <v>244</v>
+      </c>
+      <c r="D212" t="s">
+        <v>10</v>
+      </c>
+      <c r="G212" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>51</v>
+      </c>
+      <c r="B213" t="s">
+        <v>54</v>
+      </c>
+      <c r="C213" t="s">
+        <v>245</v>
+      </c>
+      <c r="D213" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>51</v>
+      </c>
+      <c r="B214" t="s">
+        <v>56</v>
+      </c>
+      <c r="C214" t="s">
+        <v>246</v>
+      </c>
+      <c r="D214" t="s">
+        <v>10</v>
+      </c>
+      <c r="G214" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>51</v>
+      </c>
+      <c r="B215" t="s">
+        <v>61</v>
+      </c>
+      <c r="C215" t="s">
+        <v>247</v>
+      </c>
+      <c r="D215" t="s">
+        <v>10</v>
+      </c>
+      <c r="G215" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>51</v>
+      </c>
+      <c r="B216" t="s">
+        <v>63</v>
+      </c>
+      <c r="C216" t="s">
+        <v>248</v>
+      </c>
+      <c r="D216" t="s">
+        <v>10</v>
+      </c>
+      <c r="G216" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>51</v>
+      </c>
+      <c r="B217" t="s">
+        <v>115</v>
+      </c>
+      <c r="C217" t="s">
+        <v>249</v>
+      </c>
+      <c r="D217" t="s">
+        <v>10</v>
+      </c>
+      <c r="G217" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>51</v>
+      </c>
+      <c r="B218" t="s">
+        <v>81</v>
+      </c>
+      <c r="C218" t="s">
+        <v>250</v>
+      </c>
+      <c r="D218" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>43</v>
+      </c>
+      <c r="B219" t="s">
+        <v>44</v>
+      </c>
+      <c r="C219" t="s">
+        <v>251</v>
+      </c>
+      <c r="D219" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>43</v>
+      </c>
+      <c r="B220" t="s">
+        <v>44</v>
+      </c>
+      <c r="C220" t="s">
+        <v>252</v>
+      </c>
+      <c r="D220" t="s">
+        <v>10</v>
+      </c>
+      <c r="G220" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>43</v>
+      </c>
+      <c r="B221" t="s">
+        <v>253</v>
+      </c>
+      <c r="C221" t="s">
+        <v>254</v>
+      </c>
+      <c r="D221" t="s">
+        <v>255</v>
+      </c>
+      <c r="G221" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>43</v>
+      </c>
+      <c r="B222" t="s">
+        <v>44</v>
+      </c>
+      <c r="C222" t="s">
+        <v>256</v>
+      </c>
+      <c r="D222" t="s">
+        <v>10</v>
+      </c>
+      <c r="G222" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>43</v>
+      </c>
+      <c r="B223" t="s">
+        <v>44</v>
+      </c>
+      <c r="C223" t="s">
+        <v>257</v>
+      </c>
+      <c r="D223" t="s">
+        <v>10</v>
+      </c>
+      <c r="G223" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>43</v>
+      </c>
+      <c r="B224" t="s">
+        <v>44</v>
+      </c>
+      <c r="C224" t="s">
+        <v>258</v>
+      </c>
+      <c r="D224" t="s">
+        <v>10</v>
+      </c>
+      <c r="G224" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>43</v>
+      </c>
+      <c r="B225" t="s">
+        <v>44</v>
+      </c>
+      <c r="C225" t="s">
+        <v>259</v>
+      </c>
+      <c r="D225" t="s">
+        <v>10</v>
+      </c>
+      <c r="G225" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>43</v>
+      </c>
+      <c r="B226" t="s">
+        <v>44</v>
+      </c>
+      <c r="C226" t="s">
+        <v>260</v>
+      </c>
+      <c r="D226" t="s">
+        <v>10</v>
+      </c>
+      <c r="G226" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>43</v>
+      </c>
+      <c r="B227" t="s">
+        <v>44</v>
+      </c>
+      <c r="C227" t="s">
+        <v>261</v>
+      </c>
+      <c r="D227" t="s">
+        <v>10</v>
+      </c>
+      <c r="G227" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>43</v>
+      </c>
+      <c r="B228" t="s">
+        <v>44</v>
+      </c>
+      <c r="C228" t="s">
+        <v>262</v>
+      </c>
+      <c r="D228" t="s">
+        <v>10</v>
+      </c>
+      <c r="G228" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>43</v>
+      </c>
+      <c r="B229" t="s">
+        <v>44</v>
+      </c>
+      <c r="C229" t="s">
+        <v>263</v>
+      </c>
+      <c r="D229" t="s">
+        <v>10</v>
+      </c>
+      <c r="G229" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>43</v>
+      </c>
+      <c r="B230" t="s">
+        <v>44</v>
+      </c>
+      <c r="C230" t="s">
+        <v>264</v>
+      </c>
+      <c r="D230" t="s">
+        <v>10</v>
+      </c>
+      <c r="G230" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>43</v>
+      </c>
+      <c r="B231" t="s">
+        <v>44</v>
+      </c>
+      <c r="C231" t="s">
+        <v>265</v>
+      </c>
+      <c r="D231" t="s">
+        <v>10</v>
+      </c>
+      <c r="G231" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>43</v>
+      </c>
+      <c r="B232" t="s">
+        <v>44</v>
+      </c>
+      <c r="C232" t="s">
+        <v>266</v>
+      </c>
+      <c r="D232" t="s">
+        <v>10</v>
+      </c>
+      <c r="G232" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>43</v>
+      </c>
+      <c r="B233" t="s">
+        <v>44</v>
+      </c>
+      <c r="C233" t="s">
+        <v>267</v>
+      </c>
+      <c r="D233" t="s">
+        <v>10</v>
+      </c>
+      <c r="G233" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>43</v>
+      </c>
+      <c r="B234" t="s">
+        <v>44</v>
+      </c>
+      <c r="C234" t="s">
+        <v>268</v>
+      </c>
+      <c r="D234" t="s">
+        <v>10</v>
+      </c>
+      <c r="G234" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>43</v>
+      </c>
+      <c r="B235" t="s">
+        <v>44</v>
+      </c>
+      <c r="C235" t="s">
+        <v>269</v>
+      </c>
+      <c r="D235" t="s">
+        <v>10</v>
+      </c>
+      <c r="G235" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>43</v>
+      </c>
+      <c r="B236" t="s">
+        <v>44</v>
+      </c>
+      <c r="C236" t="s">
+        <v>270</v>
+      </c>
+      <c r="D236" t="s">
+        <v>10</v>
+      </c>
+      <c r="G236" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>43</v>
+      </c>
+      <c r="B237" t="s">
+        <v>44</v>
+      </c>
+      <c r="C237" t="s">
+        <v>271</v>
+      </c>
+      <c r="D237" t="s">
+        <v>10</v>
+      </c>
+      <c r="G237" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>43</v>
+      </c>
+      <c r="B238" t="s">
+        <v>44</v>
+      </c>
+      <c r="C238" t="s">
+        <v>272</v>
+      </c>
+      <c r="D238" t="s">
+        <v>10</v>
+      </c>
+      <c r="G238" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>43</v>
+      </c>
+      <c r="B239" t="s">
+        <v>44</v>
+      </c>
+      <c r="C239" t="s">
+        <v>273</v>
+      </c>
+      <c r="D239" t="s">
+        <v>10</v>
+      </c>
+      <c r="G239" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>43</v>
+      </c>
+      <c r="B240" t="s">
+        <v>44</v>
+      </c>
+      <c r="C240" t="s">
+        <v>274</v>
+      </c>
+      <c r="D240" t="s">
+        <v>10</v>
+      </c>
+      <c r="G240" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>43</v>
+      </c>
+      <c r="B241" t="s">
+        <v>44</v>
+      </c>
+      <c r="C241" t="s">
+        <v>275</v>
+      </c>
+      <c r="D241" t="s">
+        <v>10</v>
+      </c>
+      <c r="G241" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>43</v>
+      </c>
+      <c r="B242" t="s">
+        <v>276</v>
+      </c>
+      <c r="C242" t="s">
+        <v>277</v>
+      </c>
+      <c r="D242" t="s">
+        <v>10</v>
+      </c>
+      <c r="G242" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
         <v>7</v>
       </c>
-      <c r="B29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" t="s">
-        <v>145</v>
-      </c>
-      <c r="F29" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B243" t="s">
+        <v>278</v>
+      </c>
+      <c r="C243" t="s">
+        <v>279</v>
+      </c>
+      <c r="D243" t="s">
+        <v>280</v>
+      </c>
+      <c r="E243" t="s">
+        <v>281</v>
+      </c>
+      <c r="F243" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
         <v>7</v>
       </c>
-      <c r="B30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" t="s">
-        <v>145</v>
-      </c>
-      <c r="F30" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B244" t="s">
+        <v>278</v>
+      </c>
+      <c r="C244" t="s">
+        <v>283</v>
+      </c>
+      <c r="D244" t="s">
+        <v>284</v>
+      </c>
+      <c r="E244" t="s">
+        <v>281</v>
+      </c>
+      <c r="F244" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
         <v>7</v>
       </c>
-      <c r="B31" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" t="s">
-        <v>145</v>
-      </c>
-      <c r="F31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B245" t="s">
+        <v>285</v>
+      </c>
+      <c r="C245" t="s">
+        <v>286</v>
+      </c>
+      <c r="D245" t="s">
+        <v>280</v>
+      </c>
+      <c r="E245" t="s">
+        <v>281</v>
+      </c>
+      <c r="F245" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
         <v>7</v>
       </c>
-      <c r="B32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B246" t="s">
+        <v>287</v>
+      </c>
+      <c r="C246" t="s">
+        <v>288</v>
+      </c>
+      <c r="D246" t="s">
+        <v>280</v>
+      </c>
+      <c r="E246" t="s">
+        <v>281</v>
+      </c>
+      <c r="F246" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>7</v>
+      </c>
+      <c r="B247" t="s">
+        <v>287</v>
+      </c>
+      <c r="C247" t="s">
+        <v>289</v>
+      </c>
+      <c r="D247" t="s">
+        <v>280</v>
+      </c>
+      <c r="E247" t="s">
+        <v>281</v>
+      </c>
+      <c r="F247" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>7</v>
+      </c>
+      <c r="B248" t="s">
+        <v>290</v>
+      </c>
+      <c r="C248" t="s">
+        <v>291</v>
+      </c>
+      <c r="D248" t="s">
+        <v>292</v>
+      </c>
+      <c r="E248" t="s">
+        <v>292</v>
+      </c>
+      <c r="F248" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>7</v>
+      </c>
+      <c r="B249" t="s">
+        <v>293</v>
+      </c>
+      <c r="C249" t="s">
+        <v>294</v>
+      </c>
+      <c r="D249" t="s">
+        <v>292</v>
+      </c>
+      <c r="E249" t="s">
+        <v>292</v>
+      </c>
+      <c r="F249" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>7</v>
+      </c>
+      <c r="B250" t="s">
+        <v>295</v>
+      </c>
+      <c r="C250" t="s">
+        <v>296</v>
+      </c>
+      <c r="D250" t="s">
+        <v>284</v>
+      </c>
+      <c r="E250" t="s">
+        <v>281</v>
+      </c>
+      <c r="F250" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>7</v>
+      </c>
+      <c r="B251" t="s">
+        <v>295</v>
+      </c>
+      <c r="C251" t="s">
+        <v>297</v>
+      </c>
+      <c r="D251" t="s">
+        <v>284</v>
+      </c>
+      <c r="E251" t="s">
+        <v>281</v>
+      </c>
+      <c r="F251" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>7</v>
+      </c>
+      <c r="B252" t="s">
+        <v>24</v>
+      </c>
+      <c r="C252" t="s">
+        <v>298</v>
+      </c>
+      <c r="D252" t="s">
+        <v>299</v>
+      </c>
+      <c r="E252" t="s">
+        <v>300</v>
+      </c>
+      <c r="F252" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>7</v>
+      </c>
+      <c r="B253" t="s">
+        <v>293</v>
+      </c>
+      <c r="C253" t="s">
+        <v>301</v>
+      </c>
+      <c r="D253" t="s">
+        <v>299</v>
+      </c>
+      <c r="E253" t="s">
+        <v>300</v>
+      </c>
+      <c r="F253" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>7</v>
+      </c>
+      <c r="B254" t="s">
+        <v>293</v>
+      </c>
+      <c r="C254" t="s">
+        <v>302</v>
+      </c>
+      <c r="D254" t="s">
+        <v>299</v>
+      </c>
+      <c r="E254" t="s">
+        <v>300</v>
+      </c>
+      <c r="F254" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>7</v>
+      </c>
+      <c r="B255" t="s">
+        <v>303</v>
+      </c>
+      <c r="C255" t="s">
+        <v>304</v>
+      </c>
+      <c r="D255" t="s">
+        <v>305</v>
+      </c>
+      <c r="E255" t="s">
+        <v>300</v>
+      </c>
+      <c r="F255" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>7</v>
+      </c>
+      <c r="B256" t="s">
+        <v>303</v>
+      </c>
+      <c r="C256" t="s">
+        <v>306</v>
+      </c>
+      <c r="D256" t="s">
+        <v>10</v>
+      </c>
+      <c r="E256" t="s">
+        <v>300</v>
+      </c>
+      <c r="F256" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>7</v>
+      </c>
+      <c r="B257" t="s">
+        <v>24</v>
+      </c>
+      <c r="C257" t="s">
+        <v>307</v>
+      </c>
+      <c r="D257" t="s">
+        <v>308</v>
+      </c>
+      <c r="E257" t="s">
+        <v>308</v>
+      </c>
+      <c r="F257" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>7</v>
+      </c>
+      <c r="B258" t="s">
+        <v>309</v>
+      </c>
+      <c r="C258" t="s">
+        <v>310</v>
+      </c>
+      <c r="D258" t="s">
+        <v>308</v>
+      </c>
+      <c r="E258" t="s">
+        <v>308</v>
+      </c>
+      <c r="F258" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>7</v>
+      </c>
+      <c r="B259" t="s">
+        <v>311</v>
+      </c>
+      <c r="C259" t="s">
+        <v>312</v>
+      </c>
+      <c r="D259" t="s">
+        <v>313</v>
+      </c>
+      <c r="E259" t="s">
+        <v>284</v>
+      </c>
+      <c r="F259" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>7</v>
+      </c>
+      <c r="B260" t="s">
+        <v>14</v>
+      </c>
+      <c r="C260" t="s">
+        <v>314</v>
+      </c>
+      <c r="D260" t="s">
+        <v>10</v>
+      </c>
+      <c r="F260" t="s">
+        <v>282</v>
+      </c>
+      <c r="G260" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>7</v>
+      </c>
+      <c r="B261" t="s">
+        <v>24</v>
+      </c>
+      <c r="C261" t="s">
+        <v>315</v>
+      </c>
+      <c r="D261" t="s">
+        <v>10</v>
+      </c>
+      <c r="E261" t="s">
+        <v>316</v>
+      </c>
+      <c r="F261" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>7</v>
+      </c>
+      <c r="B262" t="s">
+        <v>309</v>
+      </c>
+      <c r="C262" t="s">
+        <v>317</v>
+      </c>
+      <c r="D262" t="s">
+        <v>10</v>
+      </c>
+      <c r="E262" t="s">
+        <v>316</v>
+      </c>
+      <c r="F262" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>7</v>
+      </c>
+      <c r="B263" t="s">
+        <v>278</v>
+      </c>
+      <c r="C263" t="s">
+        <v>318</v>
+      </c>
+      <c r="D263" t="s">
+        <v>284</v>
+      </c>
+      <c r="E263" t="s">
+        <v>319</v>
+      </c>
+      <c r="F263" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>7</v>
+      </c>
+      <c r="B264" t="s">
+        <v>287</v>
+      </c>
+      <c r="C264" t="s">
+        <v>320</v>
+      </c>
+      <c r="D264" t="s">
+        <v>319</v>
+      </c>
+      <c r="E264" t="s">
+        <v>319</v>
+      </c>
+      <c r="F264" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>7</v>
+      </c>
+      <c r="B265" t="s">
+        <v>24</v>
+      </c>
+      <c r="C265" t="s">
+        <v>321</v>
+      </c>
+      <c r="D265" t="s">
+        <v>299</v>
+      </c>
+      <c r="E265" t="s">
+        <v>322</v>
+      </c>
+      <c r="F265" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>7</v>
+      </c>
+      <c r="B266" t="s">
+        <v>295</v>
+      </c>
+      <c r="C266" t="s">
+        <v>323</v>
+      </c>
+      <c r="D266" t="s">
+        <v>319</v>
+      </c>
+      <c r="E266" t="s">
+        <v>319</v>
+      </c>
+      <c r="F266" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>7</v>
+      </c>
+      <c r="B267" t="s">
+        <v>285</v>
+      </c>
+      <c r="C267" t="s">
+        <v>324</v>
+      </c>
+      <c r="D267" t="s">
+        <v>319</v>
+      </c>
+      <c r="E267" t="s">
+        <v>325</v>
+      </c>
+      <c r="F267" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>7</v>
+      </c>
+      <c r="B268" t="s">
+        <v>287</v>
+      </c>
+      <c r="C268" t="s">
+        <v>326</v>
+      </c>
+      <c r="D268" t="s">
+        <v>319</v>
+      </c>
+      <c r="E268" t="s">
+        <v>325</v>
+      </c>
+      <c r="F268" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>7</v>
+      </c>
+      <c r="B269" t="s">
+        <v>327</v>
+      </c>
+      <c r="C269" t="s">
+        <v>328</v>
+      </c>
+      <c r="D269" t="s">
+        <v>284</v>
+      </c>
+      <c r="F269" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>7</v>
+      </c>
+      <c r="B270" t="s">
+        <v>14</v>
+      </c>
+      <c r="C270" t="s">
+        <v>329</v>
+      </c>
+      <c r="D270" t="s">
+        <v>10</v>
+      </c>
+      <c r="E270" t="s">
+        <v>316</v>
+      </c>
+      <c r="F270" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>7</v>
+      </c>
+      <c r="B271" t="s">
+        <v>285</v>
+      </c>
+      <c r="C271" t="s">
+        <v>330</v>
+      </c>
+      <c r="D271" t="s">
+        <v>331</v>
+      </c>
+      <c r="E271" t="s">
+        <v>331</v>
+      </c>
+      <c r="F271" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>7</v>
+      </c>
+      <c r="B272" t="s">
+        <v>287</v>
+      </c>
+      <c r="C272" t="s">
+        <v>332</v>
+      </c>
+      <c r="D272" t="s">
+        <v>305</v>
+      </c>
+      <c r="E272" t="s">
+        <v>331</v>
+      </c>
+      <c r="F272" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>7</v>
+      </c>
+      <c r="B273" t="s">
+        <v>287</v>
+      </c>
+      <c r="C273" t="s">
+        <v>333</v>
+      </c>
+      <c r="D273" t="s">
+        <v>331</v>
+      </c>
+      <c r="E273" t="s">
+        <v>331</v>
+      </c>
+      <c r="F273" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>7</v>
+      </c>
+      <c r="B274" t="s">
+        <v>334</v>
+      </c>
+      <c r="C274" t="s">
+        <v>335</v>
+      </c>
+      <c r="D274" t="s">
+        <v>284</v>
+      </c>
+      <c r="E274" t="s">
+        <v>336</v>
+      </c>
+      <c r="F274" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>7</v>
+      </c>
+      <c r="B275" t="s">
+        <v>287</v>
+      </c>
+      <c r="C275" t="s">
+        <v>337</v>
+      </c>
+      <c r="D275" t="s">
+        <v>284</v>
+      </c>
+      <c r="E275" t="s">
+        <v>336</v>
+      </c>
+      <c r="F275" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>7</v>
+      </c>
+      <c r="B276" t="s">
+        <v>338</v>
+      </c>
+      <c r="C276" t="s">
+        <v>339</v>
+      </c>
+      <c r="D276" t="s">
+        <v>340</v>
+      </c>
+      <c r="E276" t="s">
+        <v>340</v>
+      </c>
+      <c r="F276" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>7</v>
+      </c>
+      <c r="B277" t="s">
+        <v>341</v>
+      </c>
+      <c r="C277" t="s">
+        <v>342</v>
+      </c>
+      <c r="D277" t="s">
+        <v>340</v>
+      </c>
+      <c r="E277" t="s">
+        <v>340</v>
+      </c>
+      <c r="F277" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>7</v>
+      </c>
+      <c r="B278" t="s">
+        <v>343</v>
+      </c>
+      <c r="C278" t="s">
+        <v>344</v>
+      </c>
+      <c r="D278" t="s">
+        <v>322</v>
+      </c>
+      <c r="E278" t="s">
+        <v>322</v>
+      </c>
+      <c r="F278" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>7</v>
+      </c>
+      <c r="B279" t="s">
+        <v>309</v>
+      </c>
+      <c r="C279" t="s">
+        <v>345</v>
+      </c>
+      <c r="D279" t="s">
+        <v>322</v>
+      </c>
+      <c r="E279" t="s">
+        <v>322</v>
+      </c>
+      <c r="F279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>7</v>
+      </c>
+      <c r="B280" t="s">
+        <v>309</v>
+      </c>
+      <c r="C280" t="s">
+        <v>346</v>
+      </c>
+      <c r="D280" t="s">
+        <v>322</v>
+      </c>
+      <c r="E280" t="s">
+        <v>322</v>
+      </c>
+      <c r="F280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>7</v>
+      </c>
+      <c r="B281" t="s">
+        <v>309</v>
+      </c>
+      <c r="C281" t="s">
+        <v>347</v>
+      </c>
+      <c r="D281" t="s">
+        <v>322</v>
+      </c>
+      <c r="E281" t="s">
+        <v>322</v>
+      </c>
+      <c r="F281" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>7</v>
+      </c>
+      <c r="B282" t="s">
+        <v>309</v>
+      </c>
+      <c r="C282" t="s">
+        <v>348</v>
+      </c>
+      <c r="D282" t="s">
+        <v>322</v>
+      </c>
+      <c r="E282" t="s">
+        <v>322</v>
+      </c>
+      <c r="F282" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>7</v>
+      </c>
+      <c r="B283" t="s">
+        <v>327</v>
+      </c>
+      <c r="C283" t="s">
+        <v>349</v>
+      </c>
+      <c r="D283" t="s">
+        <v>284</v>
+      </c>
+      <c r="E283" t="s">
+        <v>350</v>
+      </c>
+      <c r="F283" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>7</v>
+      </c>
+      <c r="B284" t="s">
+        <v>327</v>
+      </c>
+      <c r="C284" t="s">
+        <v>351</v>
+      </c>
+      <c r="D284" t="s">
+        <v>352</v>
+      </c>
+      <c r="E284" t="s">
+        <v>352</v>
+      </c>
+      <c r="F284" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>7</v>
+      </c>
+      <c r="B285" t="s">
+        <v>327</v>
+      </c>
+      <c r="C285" t="s">
+        <v>353</v>
+      </c>
+      <c r="D285" t="s">
+        <v>352</v>
+      </c>
+      <c r="E285" t="s">
+        <v>352</v>
+      </c>
+      <c r="F285" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>7</v>
+      </c>
+      <c r="B286" t="s">
+        <v>327</v>
+      </c>
+      <c r="C286" t="s">
+        <v>354</v>
+      </c>
+      <c r="D286" t="s">
+        <v>313</v>
+      </c>
+      <c r="F286" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>7</v>
+      </c>
+      <c r="B287" t="s">
+        <v>355</v>
+      </c>
+      <c r="C287" t="s">
+        <v>356</v>
+      </c>
+      <c r="D287" t="s">
+        <v>284</v>
+      </c>
+      <c r="F287" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>7</v>
+      </c>
+      <c r="B288" t="s">
+        <v>278</v>
+      </c>
+      <c r="C288" t="s">
+        <v>357</v>
+      </c>
+      <c r="D288" t="s">
+        <v>292</v>
+      </c>
+      <c r="E288" t="s">
+        <v>292</v>
+      </c>
+      <c r="F288" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>7</v>
+      </c>
+      <c r="B289" t="s">
+        <v>278</v>
+      </c>
+      <c r="C289" t="s">
+        <v>358</v>
+      </c>
+      <c r="D289" t="s">
+        <v>299</v>
+      </c>
+      <c r="E289" t="s">
+        <v>359</v>
+      </c>
+      <c r="F289" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>7</v>
+      </c>
+      <c r="B290" t="s">
+        <v>287</v>
+      </c>
+      <c r="C290" t="s">
+        <v>360</v>
+      </c>
+      <c r="D290" t="s">
+        <v>299</v>
+      </c>
+      <c r="E290" t="s">
+        <v>359</v>
+      </c>
+      <c r="F290" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>7</v>
+      </c>
+      <c r="B291" t="s">
+        <v>361</v>
+      </c>
+      <c r="C291" t="s">
+        <v>362</v>
+      </c>
+      <c r="D291" t="s">
+        <v>299</v>
+      </c>
+      <c r="E291" t="s">
+        <v>359</v>
+      </c>
+      <c r="F291" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>7</v>
+      </c>
+      <c r="B292" t="s">
+        <v>363</v>
+      </c>
+      <c r="C292" t="s">
+        <v>364</v>
+      </c>
+      <c r="D292" t="s">
+        <v>292</v>
+      </c>
+      <c r="E292" t="s">
+        <v>292</v>
+      </c>
+      <c r="F292" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>7</v>
+      </c>
+      <c r="B293" t="s">
+        <v>334</v>
+      </c>
+      <c r="C293" t="s">
+        <v>365</v>
+      </c>
+      <c r="D293" t="s">
+        <v>284</v>
+      </c>
+      <c r="E293" t="s">
+        <v>366</v>
+      </c>
+      <c r="F293" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>7</v>
+      </c>
+      <c r="B294" t="s">
+        <v>287</v>
+      </c>
+      <c r="C294" t="s">
+        <v>367</v>
+      </c>
+      <c r="D294" t="s">
+        <v>299</v>
+      </c>
+      <c r="E294" t="s">
+        <v>366</v>
+      </c>
+      <c r="F294" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>7</v>
+      </c>
+      <c r="B295" t="s">
+        <v>368</v>
+      </c>
+      <c r="C295" t="s">
+        <v>369</v>
+      </c>
+      <c r="D295" t="s">
+        <v>284</v>
+      </c>
+      <c r="E295" t="s">
+        <v>284</v>
+      </c>
+      <c r="F295" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>7</v>
+      </c>
+      <c r="B296" t="s">
+        <v>355</v>
+      </c>
+      <c r="C296" t="s">
+        <v>370</v>
+      </c>
+      <c r="D296" t="s">
+        <v>284</v>
+      </c>
+      <c r="E296" t="s">
+        <v>371</v>
+      </c>
+      <c r="F296" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>7</v>
+      </c>
+      <c r="B297" t="s">
+        <v>287</v>
+      </c>
+      <c r="C297" t="s">
+        <v>372</v>
+      </c>
+      <c r="D297" t="s">
+        <v>284</v>
+      </c>
+      <c r="E297" t="s">
+        <v>371</v>
+      </c>
+      <c r="F297" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
         <v>43</v>
       </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" t="s">
-        <v>145</v>
-      </c>
-      <c r="F32" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B298" t="s">
+        <v>373</v>
+      </c>
+      <c r="C298" t="s">
+        <v>374</v>
+      </c>
+      <c r="D298" t="s">
+        <v>375</v>
+      </c>
+      <c r="E298" t="s">
+        <v>375</v>
+      </c>
+      <c r="F298" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
         <v>43</v>
       </c>
-      <c r="D33" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" t="s">
-        <v>145</v>
-      </c>
-      <c r="F33" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B299" t="s">
+        <v>373</v>
+      </c>
+      <c r="C299" t="s">
+        <v>376</v>
+      </c>
+      <c r="D299" t="s">
+        <v>375</v>
+      </c>
+      <c r="E299" t="s">
+        <v>375</v>
+      </c>
+      <c r="F299" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>43</v>
+      </c>
+      <c r="B300" t="s">
+        <v>373</v>
+      </c>
+      <c r="C300" t="s">
+        <v>377</v>
+      </c>
+      <c r="D300" t="s">
+        <v>375</v>
+      </c>
+      <c r="E300" t="s">
+        <v>375</v>
+      </c>
+      <c r="F300" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>43</v>
+      </c>
+      <c r="B301" t="s">
+        <v>373</v>
+      </c>
+      <c r="C301" t="s">
+        <v>378</v>
+      </c>
+      <c r="D301" t="s">
+        <v>375</v>
+      </c>
+      <c r="E301" t="s">
+        <v>375</v>
+      </c>
+      <c r="F301" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>43</v>
+      </c>
+      <c r="B302" t="s">
+        <v>373</v>
+      </c>
+      <c r="C302" t="s">
+        <v>379</v>
+      </c>
+      <c r="D302" t="s">
+        <v>375</v>
+      </c>
+      <c r="E302" t="s">
+        <v>375</v>
+      </c>
+      <c r="F302" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>43</v>
+      </c>
+      <c r="B303" t="s">
+        <v>373</v>
+      </c>
+      <c r="C303" t="s">
+        <v>380</v>
+      </c>
+      <c r="D303" t="s">
+        <v>375</v>
+      </c>
+      <c r="E303" t="s">
+        <v>375</v>
+      </c>
+      <c r="F303" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>43</v>
+      </c>
+      <c r="B304" t="s">
+        <v>253</v>
+      </c>
+      <c r="C304" t="s">
+        <v>381</v>
+      </c>
+      <c r="D304" t="s">
+        <v>255</v>
+      </c>
+      <c r="E304" t="s">
+        <v>382</v>
+      </c>
+      <c r="F304" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>43</v>
+      </c>
+      <c r="B305" t="s">
+        <v>383</v>
+      </c>
+      <c r="C305" t="s">
+        <v>384</v>
+      </c>
+      <c r="D305" t="s">
+        <v>299</v>
+      </c>
+      <c r="E305" t="s">
+        <v>385</v>
+      </c>
+      <c r="F305" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>43</v>
+      </c>
+      <c r="B306" t="s">
+        <v>386</v>
+      </c>
+      <c r="C306" t="s">
+        <v>387</v>
+      </c>
+      <c r="D306" t="s">
+        <v>388</v>
+      </c>
+      <c r="E306" t="s">
+        <v>388</v>
+      </c>
+      <c r="F306" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>43</v>
+      </c>
+      <c r="B307" t="s">
+        <v>373</v>
+      </c>
+      <c r="C307" t="s">
+        <v>389</v>
+      </c>
+      <c r="D307" t="s">
+        <v>388</v>
+      </c>
+      <c r="E307" t="s">
+        <v>388</v>
+      </c>
+      <c r="F307" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>43</v>
+      </c>
+      <c r="B308" t="s">
         <v>44</v>
       </c>
-      <c r="D34" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" t="s">
-        <v>145</v>
-      </c>
-      <c r="F34" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="C308" t="s">
+        <v>390</v>
+      </c>
+      <c r="D308" t="s">
+        <v>10</v>
+      </c>
+      <c r="G308" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>43</v>
+      </c>
+      <c r="B309" t="s">
+        <v>253</v>
+      </c>
+      <c r="C309" t="s">
+        <v>391</v>
+      </c>
+      <c r="D309" t="s">
+        <v>255</v>
+      </c>
+      <c r="E309" t="s">
+        <v>392</v>
+      </c>
+      <c r="F309" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>43</v>
+      </c>
+      <c r="B310" t="s">
+        <v>386</v>
+      </c>
+      <c r="C310" t="s">
+        <v>393</v>
+      </c>
+      <c r="D310" t="s">
+        <v>299</v>
+      </c>
+      <c r="E310" t="s">
+        <v>375</v>
+      </c>
+      <c r="F310" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>43</v>
+      </c>
+      <c r="B311" t="s">
+        <v>386</v>
+      </c>
+      <c r="C311" t="s">
+        <v>394</v>
+      </c>
+      <c r="D311" t="s">
+        <v>299</v>
+      </c>
+      <c r="E311" t="s">
+        <v>375</v>
+      </c>
+      <c r="F311" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>43</v>
+      </c>
+      <c r="B312" t="s">
+        <v>386</v>
+      </c>
+      <c r="C312" t="s">
+        <v>395</v>
+      </c>
+      <c r="D312" t="s">
+        <v>299</v>
+      </c>
+      <c r="E312" t="s">
+        <v>375</v>
+      </c>
+      <c r="F312" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>43</v>
+      </c>
+      <c r="B313" t="s">
+        <v>386</v>
+      </c>
+      <c r="C313" t="s">
+        <v>396</v>
+      </c>
+      <c r="D313" t="s">
+        <v>299</v>
+      </c>
+      <c r="E313" t="s">
+        <v>397</v>
+      </c>
+      <c r="F313" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>43</v>
+      </c>
+      <c r="B314" t="s">
+        <v>383</v>
+      </c>
+      <c r="C314" t="s">
+        <v>398</v>
+      </c>
+      <c r="D314" t="s">
+        <v>399</v>
+      </c>
+      <c r="E314" t="s">
+        <v>399</v>
+      </c>
+      <c r="F314" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>43</v>
+      </c>
+      <c r="B315" t="s">
+        <v>383</v>
+      </c>
+      <c r="C315" t="s">
+        <v>400</v>
+      </c>
+      <c r="D315" t="s">
+        <v>399</v>
+      </c>
+      <c r="E315" t="s">
+        <v>399</v>
+      </c>
+      <c r="F315" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>43</v>
+      </c>
+      <c r="B316" t="s">
+        <v>383</v>
+      </c>
+      <c r="C316" t="s">
+        <v>401</v>
+      </c>
+      <c r="D316" t="s">
+        <v>399</v>
+      </c>
+      <c r="E316" t="s">
+        <v>399</v>
+      </c>
+      <c r="F316" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>43</v>
+      </c>
+      <c r="B317" t="s">
+        <v>402</v>
+      </c>
+      <c r="C317" t="s">
+        <v>403</v>
+      </c>
+      <c r="D317" t="s">
+        <v>399</v>
+      </c>
+      <c r="E317" t="s">
+        <v>399</v>
+      </c>
+      <c r="F317" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>43</v>
+      </c>
+      <c r="B318" t="s">
         <v>44</v>
       </c>
-      <c r="D35" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" t="s">
-        <v>145</v>
-      </c>
-      <c r="F35" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" t="s">
-        <v>145</v>
-      </c>
-      <c r="F36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" t="s">
-        <v>145</v>
-      </c>
-      <c r="F37" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" t="s">
-        <v>48</v>
-      </c>
-      <c r="F38" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" t="s">
-        <v>48</v>
-      </c>
-      <c r="F39" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" t="s">
-        <v>50</v>
-      </c>
-      <c r="D42" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" t="s">
-        <v>51</v>
-      </c>
-      <c r="F42" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" t="s">
-        <v>21</v>
-      </c>
-      <c r="C43" t="s">
-        <v>50</v>
-      </c>
-      <c r="D43" t="s">
-        <v>51</v>
-      </c>
-      <c r="E43" t="s">
-        <v>51</v>
-      </c>
-      <c r="F43" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" t="s">
-        <v>53</v>
-      </c>
-      <c r="F44" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" t="s">
-        <v>53</v>
-      </c>
-      <c r="F45" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" t="s">
-        <v>53</v>
-      </c>
-      <c r="F46" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" t="s">
-        <v>53</v>
-      </c>
-      <c r="F47" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" t="s">
-        <v>53</v>
-      </c>
-      <c r="F48" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" t="s">
-        <v>54</v>
-      </c>
-      <c r="D49" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" t="s">
-        <v>53</v>
-      </c>
-      <c r="F49" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" t="s">
-        <v>56</v>
-      </c>
-      <c r="C50" t="s">
-        <v>57</v>
-      </c>
-      <c r="D50" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" t="s">
-        <v>58</v>
-      </c>
-      <c r="F50" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>55</v>
-      </c>
-      <c r="B51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" t="s">
-        <v>58</v>
-      </c>
-      <c r="F51" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" t="s">
-        <v>56</v>
-      </c>
-      <c r="C52" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" t="s">
-        <v>58</v>
-      </c>
-      <c r="F52" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>55</v>
-      </c>
-      <c r="B53" t="s">
-        <v>61</v>
-      </c>
-      <c r="C53" t="s">
-        <v>62</v>
-      </c>
-      <c r="D53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" t="s">
-        <v>58</v>
-      </c>
-      <c r="F53" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" t="s">
-        <v>63</v>
-      </c>
-      <c r="C54" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" t="s">
-        <v>58</v>
-      </c>
-      <c r="F54" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" t="s">
-        <v>58</v>
-      </c>
-      <c r="F55" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56" t="s">
-        <v>64</v>
-      </c>
-      <c r="D56" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" t="s">
-        <v>65</v>
-      </c>
-      <c r="F56" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>55</v>
-      </c>
-      <c r="B57" t="s">
-        <v>63</v>
-      </c>
-      <c r="C57" t="s">
-        <v>64</v>
-      </c>
-      <c r="D57" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" t="s">
-        <v>65</v>
-      </c>
-      <c r="F57" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>55</v>
-      </c>
-      <c r="B58" t="s">
-        <v>56</v>
-      </c>
-      <c r="C58" t="s">
-        <v>64</v>
-      </c>
-      <c r="D58" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" t="s">
-        <v>65</v>
-      </c>
-      <c r="F58" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59" t="s">
-        <v>56</v>
-      </c>
-      <c r="C59" t="s">
-        <v>66</v>
-      </c>
-      <c r="D59" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" t="s">
-        <v>65</v>
-      </c>
-      <c r="F59" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" t="s">
-        <v>67</v>
-      </c>
-      <c r="D60" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" t="s">
-        <v>169</v>
-      </c>
-      <c r="F60" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61" t="s">
-        <v>67</v>
-      </c>
-      <c r="D61" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" t="s">
-        <v>169</v>
-      </c>
-      <c r="F61" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>55</v>
-      </c>
-      <c r="B62" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" t="s">
-        <v>169</v>
-      </c>
-      <c r="F62" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" t="s">
-        <v>69</v>
-      </c>
-      <c r="C63" t="s">
-        <v>67</v>
-      </c>
-      <c r="D63" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" t="s">
-        <v>169</v>
-      </c>
-      <c r="F63" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D64" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" t="s">
-        <v>169</v>
-      </c>
-      <c r="F64" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" t="s">
-        <v>56</v>
-      </c>
-      <c r="C65" t="s">
-        <v>67</v>
-      </c>
-      <c r="D65" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" t="s">
-        <v>169</v>
-      </c>
-      <c r="F65" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>55</v>
-      </c>
-      <c r="B66" t="s">
-        <v>70</v>
-      </c>
-      <c r="C66" t="s">
-        <v>71</v>
-      </c>
-      <c r="D66" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" t="s">
-        <v>72</v>
-      </c>
-      <c r="F66" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>55</v>
-      </c>
-      <c r="B67" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" t="s">
-        <v>73</v>
-      </c>
-      <c r="D67" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" t="s">
-        <v>72</v>
-      </c>
-      <c r="F67" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>55</v>
-      </c>
-      <c r="B68" t="s">
-        <v>70</v>
-      </c>
-      <c r="C68" t="s">
-        <v>74</v>
-      </c>
-      <c r="D68" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" t="s">
-        <v>169</v>
-      </c>
-      <c r="F68" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>55</v>
-      </c>
-      <c r="B69" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" t="s">
-        <v>75</v>
-      </c>
-      <c r="D69" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" t="s">
-        <v>169</v>
-      </c>
-      <c r="F69" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>55</v>
-      </c>
-      <c r="B70" t="s">
-        <v>56</v>
-      </c>
-      <c r="C70" t="s">
-        <v>76</v>
-      </c>
-      <c r="D70" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" t="s">
-        <v>169</v>
-      </c>
-      <c r="F70" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>55</v>
-      </c>
-      <c r="B71" t="s">
-        <v>56</v>
-      </c>
-      <c r="C71" t="s">
-        <v>77</v>
-      </c>
-      <c r="D71" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" t="s">
-        <v>169</v>
-      </c>
-      <c r="F71" t="s">
-        <v>20</v>
+      <c r="C318" t="s">
+        <v>404</v>
+      </c>
+      <c r="D318" t="s">
+        <v>10</v>
+      </c>
+      <c r="E318" t="s">
+        <v>405</v>
+      </c>
+      <c r="F318" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>43</v>
+      </c>
+      <c r="B319" t="s">
+        <v>253</v>
+      </c>
+      <c r="C319" t="s">
+        <v>406</v>
+      </c>
+      <c r="D319" t="s">
+        <v>407</v>
+      </c>
+      <c r="E319" t="s">
+        <v>407</v>
+      </c>
+      <c r="F319" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>43</v>
+      </c>
+      <c r="B320" t="s">
+        <v>383</v>
+      </c>
+      <c r="C320" t="s">
+        <v>408</v>
+      </c>
+      <c r="D320" t="s">
+        <v>407</v>
+      </c>
+      <c r="E320" t="s">
+        <v>407</v>
+      </c>
+      <c r="F320" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>43</v>
+      </c>
+      <c r="B321" t="s">
+        <v>409</v>
+      </c>
+      <c r="C321" t="s">
+        <v>410</v>
+      </c>
+      <c r="D321" t="s">
+        <v>411</v>
+      </c>
+      <c r="E321" t="s">
+        <v>411</v>
+      </c>
+      <c r="F321" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>43</v>
+      </c>
+      <c r="B322" t="s">
+        <v>253</v>
+      </c>
+      <c r="C322" t="s">
+        <v>412</v>
+      </c>
+      <c r="D322" t="s">
+        <v>385</v>
+      </c>
+      <c r="E322" t="s">
+        <v>385</v>
+      </c>
+      <c r="F322" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>43</v>
+      </c>
+      <c r="B323" t="s">
+        <v>383</v>
+      </c>
+      <c r="C323" t="s">
+        <v>413</v>
+      </c>
+      <c r="D323" t="s">
+        <v>385</v>
+      </c>
+      <c r="E323" t="s">
+        <v>385</v>
+      </c>
+      <c r="F323" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>43</v>
+      </c>
+      <c r="B324" t="s">
+        <v>383</v>
+      </c>
+      <c r="C324" t="s">
+        <v>414</v>
+      </c>
+      <c r="D324" t="s">
+        <v>385</v>
+      </c>
+      <c r="E324" t="s">
+        <v>385</v>
+      </c>
+      <c r="F324" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>43</v>
+      </c>
+      <c r="B325" t="s">
+        <v>373</v>
+      </c>
+      <c r="C325" t="s">
+        <v>415</v>
+      </c>
+      <c r="D325" t="s">
+        <v>416</v>
+      </c>
+      <c r="E325" t="s">
+        <v>416</v>
+      </c>
+      <c r="F325" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>43</v>
+      </c>
+      <c r="B326" t="s">
+        <v>373</v>
+      </c>
+      <c r="C326" t="s">
+        <v>417</v>
+      </c>
+      <c r="D326" t="s">
+        <v>416</v>
+      </c>
+      <c r="E326" t="s">
+        <v>416</v>
+      </c>
+      <c r="F326" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>43</v>
+      </c>
+      <c r="B327" t="s">
+        <v>44</v>
+      </c>
+      <c r="C327" t="s">
+        <v>418</v>
+      </c>
+      <c r="D327" t="s">
+        <v>10</v>
+      </c>
+      <c r="E327" t="s">
+        <v>419</v>
+      </c>
+      <c r="F327" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>43</v>
+      </c>
+      <c r="B328" t="s">
+        <v>44</v>
+      </c>
+      <c r="C328" t="s">
+        <v>420</v>
+      </c>
+      <c r="D328" t="s">
+        <v>10</v>
+      </c>
+      <c r="G328" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>43</v>
+      </c>
+      <c r="B329" t="s">
+        <v>44</v>
+      </c>
+      <c r="C329" t="s">
+        <v>421</v>
+      </c>
+      <c r="D329" t="s">
+        <v>10</v>
+      </c>
+      <c r="G329" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>43</v>
+      </c>
+      <c r="B330" t="s">
+        <v>373</v>
+      </c>
+      <c r="C330" t="s">
+        <v>422</v>
+      </c>
+      <c r="D330" t="s">
+        <v>411</v>
+      </c>
+      <c r="E330" t="s">
+        <v>411</v>
+      </c>
+      <c r="F330" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>43</v>
+      </c>
+      <c r="B331" t="s">
+        <v>373</v>
+      </c>
+      <c r="C331" t="s">
+        <v>423</v>
+      </c>
+      <c r="D331" t="s">
+        <v>411</v>
+      </c>
+      <c r="E331" t="s">
+        <v>411</v>
+      </c>
+      <c r="F331" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>43</v>
+      </c>
+      <c r="B332" t="s">
+        <v>383</v>
+      </c>
+      <c r="C332" t="s">
+        <v>424</v>
+      </c>
+      <c r="D332" t="s">
+        <v>411</v>
+      </c>
+      <c r="E332" t="s">
+        <v>411</v>
+      </c>
+      <c r="F332" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>43</v>
+      </c>
+      <c r="B333" t="s">
+        <v>383</v>
+      </c>
+      <c r="C333" t="s">
+        <v>425</v>
+      </c>
+      <c r="D333" t="s">
+        <v>411</v>
+      </c>
+      <c r="E333" t="s">
+        <v>411</v>
+      </c>
+      <c r="F333" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>43</v>
+      </c>
+      <c r="B334" t="s">
+        <v>383</v>
+      </c>
+      <c r="C334" t="s">
+        <v>426</v>
+      </c>
+      <c r="D334" t="s">
+        <v>255</v>
+      </c>
+      <c r="E334" t="s">
+        <v>392</v>
+      </c>
+      <c r="F334" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>43</v>
+      </c>
+      <c r="B335" t="s">
+        <v>383</v>
+      </c>
+      <c r="C335" t="s">
+        <v>427</v>
+      </c>
+      <c r="D335" t="s">
+        <v>255</v>
+      </c>
+      <c r="E335" t="s">
+        <v>392</v>
+      </c>
+      <c r="F335" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>43</v>
+      </c>
+      <c r="B336" t="s">
+        <v>383</v>
+      </c>
+      <c r="C336" t="s">
+        <v>428</v>
+      </c>
+      <c r="D336" t="s">
+        <v>255</v>
+      </c>
+      <c r="E336" t="s">
+        <v>392</v>
+      </c>
+      <c r="F336" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>43</v>
+      </c>
+      <c r="B337" t="s">
+        <v>383</v>
+      </c>
+      <c r="C337" t="s">
+        <v>429</v>
+      </c>
+      <c r="D337" t="s">
+        <v>255</v>
+      </c>
+      <c r="E337" t="s">
+        <v>392</v>
+      </c>
+      <c r="F337" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>43</v>
+      </c>
+      <c r="B338" t="s">
+        <v>373</v>
+      </c>
+      <c r="C338" t="s">
+        <v>430</v>
+      </c>
+      <c r="D338" t="s">
+        <v>431</v>
+      </c>
+      <c r="E338" t="s">
+        <v>432</v>
+      </c>
+      <c r="F338" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G338">
+      <sortCondition ref="G1"/>
+    </sortState>
+  </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="E44:E71 E2:E40" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E338" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>BilledeValgListe</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F71" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F338" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"X"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2392,562 +8070,562 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>444</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>95</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>98</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>455</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>106</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>107</v>
+        <v>457</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>108</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>109</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>110</v>
+        <v>459</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>460</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>461</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>462</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>114</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>416</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>464</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>319</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>117</v>
+        <v>465</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>118</v>
+        <v>466</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>467</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>468</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>58</v>
+        <v>399</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>121</v>
+        <v>469</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>123</v>
+        <v>470</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>124</v>
+        <v>471</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>125</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>407</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>126</v>
+        <v>472</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>127</v>
+        <v>473</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>128</v>
+        <v>474</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>475</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>130</v>
+        <v>476</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>131</v>
+        <v>477</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>132</v>
+        <v>478</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>133</v>
+        <v>479</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>134</v>
+        <v>480</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>135</v>
+        <v>385</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>136</v>
+        <v>481</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>137</v>
+        <v>482</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>138</v>
+        <v>483</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>139</v>
+        <v>484</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>140</v>
+        <v>485</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>141</v>
+        <v>486</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>142</v>
+        <v>487</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>143</v>
+        <v>488</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>144</v>
+        <v>489</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>145</v>
+        <v>322</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>146</v>
+        <v>490</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>147</v>
+        <v>397</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>148</v>
+        <v>491</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>48</v>
+        <v>352</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>492</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>150</v>
+        <v>493</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>151</v>
+        <v>494</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>152</v>
+        <v>419</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>153</v>
+        <v>495</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>154</v>
+        <v>359</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>155</v>
+        <v>366</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>156</v>
+        <v>496</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>157</v>
+        <v>497</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>158</v>
+        <v>498</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>159</v>
+        <v>305</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>160</v>
+        <v>499</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>161</v>
+        <v>500</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>162</v>
+        <v>501</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>163</v>
+        <v>502</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>164</v>
+        <v>503</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>165</v>
+        <v>504</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>166</v>
+        <v>505</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>167</v>
+        <v>506</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>168</v>
+        <v>507</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>169</v>
+        <v>411</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>170</v>
+        <v>508</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>171</v>
+        <v>509</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>172</v>
+        <v>510</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>173</v>
+        <v>392</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>174</v>
+        <v>511</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>175</v>
+        <v>512</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>176</v>
+        <v>513</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>177</v>
+        <v>432</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>178</v>
+        <v>514</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>179</v>
+        <v>515</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>180</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -2957,7 +8635,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2966,7 +8644,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>181</v>
+        <v>516</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2974,85 +8652,93 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>182</v>
+        <v>517</v>
       </c>
       <c r="B3" t="s">
-        <v>183</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>519</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>521</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>188</v>
+        <v>523</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>190</v>
+        <v>525</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B8" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" t="s">
-        <v>193</v>
-      </c>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>192</v>
+        <v>529</v>
       </c>
       <c r="B10" t="s">
-        <v>194</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>192</v>
+        <v>529</v>
       </c>
       <c r="B11" t="s">
-        <v>195</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>192</v>
+        <v>529</v>
       </c>
       <c r="B12" t="s">
-        <v>196</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>192</v>
+        <v>529</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>533</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B14" t="s">
+        <v>534</v>
       </c>
     </row>
   </sheetData>

--- a/data/sport_artwork_review.BACKUP.xlsx
+++ b/data/sport_artwork_review.BACKUP.xlsx
@@ -8,26 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DAECD5-987F-4EA2-A58F-47115C617FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA70A13-8F72-4F35-AC0A-1ACA796B05AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sport-artwork review" sheetId="1" r:id="rId1"/>
     <sheet name="BilledeListe" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Forsvundne (havde valg)" sheetId="3" r:id="rId3"/>
-    <sheet name="Vejledning" sheetId="4" r:id="rId4"/>
+    <sheet name="Vejledning" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sport-artwork review'!$A$1:$H$1</definedName>
-    <definedName name="BilledeValgListe">BilledeListe!$A$1:$A$117</definedName>
+    <definedName name="BilledeValgListe">BilledeListe!$A$1:$A$126</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="497">
   <si>
     <t>Kanalgruppe</t>
   </si>
@@ -113,6 +112,9 @@
     <t>TMDb</t>
   </si>
   <si>
+    <t>Danskerklubben.jpg</t>
+  </si>
+  <si>
     <t>Fodbold: Premier League-studiet</t>
   </si>
   <si>
@@ -140,6 +142,9 @@
     <t>Motorsport-generic.jpg</t>
   </si>
   <si>
+    <t>Højdepunkter fra Dansk Motorsport.jpg</t>
+  </si>
+  <si>
     <t>Ice Road Truckers</t>
   </si>
   <si>
@@ -239,6 +244,9 @@
     <t>Sky Sports: Ref Watch</t>
   </si>
   <si>
+    <t>Sky Sports Ref Watch.jpg</t>
+  </si>
+  <si>
     <t>Sky Sports: The Football Show</t>
   </si>
   <si>
@@ -290,9 +298,6 @@
     <t>Watt the F1!?</t>
   </si>
   <si>
-    <t>https://image.tmdb.org/t/p/original/A4K7y6tBXrt0RR21wnmnS8lWWJK.jpg</t>
-  </si>
-  <si>
     <t>B - TV2 Sport/TV2 Sport X/TV2</t>
   </si>
   <si>
@@ -398,9 +403,6 @@
     <t>Fodbold: Totalfodbold</t>
   </si>
   <si>
-    <t>https://image.tmdb.org/t/p/original/sV5GyKg1lGC6Kba1xRpcLis2kxQ.jpg</t>
-  </si>
-  <si>
     <t>Fra 1-værelses til strandvejsvilla</t>
   </si>
   <si>
@@ -1241,7 +1243,7 @@
     <t>DP World Tour Danish Golf Championship.jpg</t>
   </si>
   <si>
-    <t>Danskerklubben.jpg</t>
+    <t>Danskerklubben2.jpg</t>
   </si>
   <si>
     <t>EFL Championship Highligts.jpg</t>
@@ -1295,12 +1297,12 @@
     <t>Håndbold Kvindeligaen.jpg</t>
   </si>
   <si>
-    <t>Højdepunkter fra Dansk Motorsport.jpg</t>
-  </si>
-  <si>
     <t>Le Mans.jpg</t>
   </si>
   <si>
+    <t>Lets Be Frank.jpg</t>
+  </si>
+  <si>
     <t>Ligue 1 The Season Review Show.jpg</t>
   </si>
   <si>
@@ -1328,6 +1330,9 @@
     <t>NFL2.jpg</t>
   </si>
   <si>
+    <t>Onside.jpg</t>
+  </si>
+  <si>
     <t>PDC World Series of Darts.jpg</t>
   </si>
   <si>
@@ -1364,9 +1369,6 @@
     <t>Skisport.jpg</t>
   </si>
   <si>
-    <t>Sky Sports Ref Watch.jpg</t>
-  </si>
-  <si>
     <t>Snooker.jpg</t>
   </si>
   <si>
@@ -1376,6 +1378,9 @@
     <t>Sporten.jpg</t>
   </si>
   <si>
+    <t>Sportstalk.jpg</t>
+  </si>
+  <si>
     <t>Spot på Betinia Liga.jpg</t>
   </si>
   <si>
@@ -1394,6 +1399,12 @@
     <t>Tennis-generic3.jpg</t>
   </si>
   <si>
+    <t>Tirsdagstrænerne.jpg</t>
+  </si>
+  <si>
+    <t>Totalfodbold.jpg</t>
+  </si>
+  <si>
     <t>Tour Studiet.jpg</t>
   </si>
   <si>
@@ -1421,9 +1432,15 @@
     <t>VM i dressur2.jpg</t>
   </si>
   <si>
+    <t>Var-rummet.jpg</t>
+  </si>
+  <si>
     <t>Viaplay_Sport_News-generic.jpg</t>
   </si>
   <si>
+    <t>Vuelta a España -  Studiet.jpg</t>
+  </si>
+  <si>
     <t>WTA-1000.jpg</t>
   </si>
   <si>
@@ -1436,154 +1453,13 @@
     <t>WTA-generic.jpg</t>
   </si>
   <si>
+    <t>Watt the F1.jpg</t>
+  </si>
+  <si>
     <t>cykling4.jpg</t>
   </si>
   <si>
     <t>tv3sport-generic.jpg</t>
-  </si>
-  <si>
-    <t>Tidligere valgt billede</t>
-  </si>
-  <si>
-    <t>1. Division</t>
-  </si>
-  <si>
-    <t>1. Division Magasinet</t>
-  </si>
-  <si>
-    <t>1. Division: AaB - HB Køge</t>
-  </si>
-  <si>
-    <t>3F Superliga: FC Nordsjælland - Brøndby IF</t>
-  </si>
-  <si>
-    <t>Betinia LIGA</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold: Augsburg - Schalke 04</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold: Dortmund - Hamburger SV</t>
-  </si>
-  <si>
-    <t>Bundesliga Fodbold: Union Berlin - Frankfurt</t>
-  </si>
-  <si>
-    <t>Bundesliga Highlights I: Bundesliga Highlights</t>
-  </si>
-  <si>
-    <t>Bundesliga Saturday Highlights</t>
-  </si>
-  <si>
-    <t>Bundesliga Saturday Highlights: Bundesliga Highlights</t>
-  </si>
-  <si>
-    <t>Bundesliga: Augsburg - Schalke 04</t>
-  </si>
-  <si>
-    <t>Bundesliga: Dortmund - Hamburger SV</t>
-  </si>
-  <si>
-    <t>Bundesliga: Union Berlin - Frankfurt</t>
-  </si>
-  <si>
-    <t>Champions League Weekly</t>
-  </si>
-  <si>
-    <t>Champions League Weekly: UEFA Champions League Weekly</t>
-  </si>
-  <si>
-    <t>Formel 1 360°</t>
-  </si>
-  <si>
-    <t>https://image.tmdb.org/t/p/original/uzNsBqsMSkKyL4bbatvCvYYpDOj.jpg</t>
-  </si>
-  <si>
-    <t>Før Superligaen</t>
-  </si>
-  <si>
-    <t>https://image.tmdb.org/t/p/original/6TNZdG9lRP6ECdAIArYgJ5qa7kX.jpg</t>
-  </si>
-  <si>
-    <t>Før Superligaen Aarhus Gymnastikforening</t>
-  </si>
-  <si>
-    <t>Før Superligaen Brøndby IF</t>
-  </si>
-  <si>
-    <t>IndyCar: Snap-On Makers and Fixers 250 - Løb 1</t>
-  </si>
-  <si>
-    <t>IndyCar: Snap-On Makers and Fixers 250 - Løb 2</t>
-  </si>
-  <si>
-    <t>Ligue 1</t>
-  </si>
-  <si>
-    <t>Ligue 1: Monaco - Marseille</t>
-  </si>
-  <si>
-    <t>PDC European Tour</t>
-  </si>
-  <si>
-    <t>PDC European Tour: Hungarian Darts Trophy</t>
-  </si>
-  <si>
-    <t>Premier League: Bournemouth - Everton</t>
-  </si>
-  <si>
-    <t>Premier League: Chelsea - Brighton</t>
-  </si>
-  <si>
-    <t>Premier League: Leeds - Brentford</t>
-  </si>
-  <si>
-    <t>Premier League: Manchester United - Ipswich</t>
-  </si>
-  <si>
-    <t>Premier League: Tottenham - Newcastle</t>
-  </si>
-  <si>
-    <t>Superliga</t>
-  </si>
-  <si>
-    <t>Superliga Studie</t>
-  </si>
-  <si>
-    <t>Superliga Studie: FC Nordsjælland - Brøndby IF</t>
-  </si>
-  <si>
-    <t>Superliga Studie: Silkeborg IF - FC Midtjylland</t>
-  </si>
-  <si>
-    <t>Superliga: AC Horsens - Viborg FF</t>
-  </si>
-  <si>
-    <t>Superliga: FC Nordsjælland - Brøndby IF</t>
-  </si>
-  <si>
-    <t>Superliga: Silkeborg IF - FC Midtjylland</t>
-  </si>
-  <si>
-    <t>3F Superliga: Efter Randers FC-AGF</t>
-  </si>
-  <si>
-    <t>3F Superliga: Før Lyngby Boldklub-Odense Boldklub</t>
-  </si>
-  <si>
-    <t>Herreligaen: Studiet</t>
-  </si>
-  <si>
-    <t>Serie A: Juventus-Parma</t>
-  </si>
-  <si>
-    <t>VM i MTB: Elite, Cross-country, Olympisk (m)</t>
-  </si>
-  <si>
-    <t>Vuelta a España: 8. etape</t>
   </si>
   <si>
     <t>Sådan bruger du denne fil</t>
@@ -2099,10 +1975,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -2116,10 +1992,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -2133,10 +2009,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -2150,10 +2026,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -2167,10 +2043,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
@@ -2184,10 +2060,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -2201,10 +2077,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -2218,10 +2094,10 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
@@ -2235,10 +2111,10 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -2252,10 +2128,10 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -2269,10 +2145,10 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -2286,10 +2162,10 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
@@ -2303,10 +2179,10 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -2323,7 +2199,7 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
@@ -2337,10 +2213,10 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
@@ -2354,10 +2230,10 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
@@ -2371,10 +2247,10 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
@@ -2388,10 +2264,10 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
@@ -2405,10 +2281,10 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
         <v>15</v>
@@ -2422,10 +2298,10 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
         <v>15</v>
@@ -2439,10 +2315,10 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
@@ -2456,19 +2332,13 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" t="s">
-        <v>445</v>
-      </c>
-      <c r="F26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s">
         <v>12</v>
@@ -2479,10 +2349,10 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
         <v>15</v>
@@ -2496,10 +2366,10 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
         <v>15</v>
@@ -2516,7 +2386,7 @@
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
@@ -2530,13 +2400,19 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="E30" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
       </c>
       <c r="G30" t="s">
         <v>12</v>
@@ -2544,13 +2420,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
         <v>15</v>
@@ -2561,13 +2437,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
@@ -2578,13 +2454,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D33" t="s">
         <v>15</v>
@@ -2595,13 +2471,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D34" t="s">
         <v>15</v>
@@ -2612,13 +2488,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D35" t="s">
         <v>15</v>
@@ -2629,13 +2505,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
         <v>15</v>
@@ -2646,13 +2522,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
         <v>15</v>
@@ -2663,13 +2539,13 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
         <v>15</v>
@@ -2680,16 +2556,16 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="D39" t="s">
-        <v>116</v>
+        <v>15</v>
       </c>
       <c r="G39" t="s">
         <v>12</v>
@@ -2697,13 +2573,13 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="D40" t="s">
         <v>15</v>
@@ -2714,13 +2590,13 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D41" t="s">
         <v>15</v>
@@ -2731,13 +2607,13 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C42" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D42" t="s">
         <v>15</v>
@@ -2748,16 +2624,16 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="G43" t="s">
         <v>12</v>
@@ -2765,13 +2641,13 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C44" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D44" t="s">
         <v>15</v>
@@ -2782,13 +2658,13 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C45" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D45" t="s">
         <v>15</v>
@@ -2799,13 +2675,13 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="D46" t="s">
         <v>15</v>
@@ -2816,13 +2692,13 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C47" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="D47" t="s">
         <v>15</v>
@@ -2833,13 +2709,13 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B48" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C48" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
         <v>15</v>
@@ -2850,13 +2726,13 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C49" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="D49" t="s">
         <v>15</v>
@@ -2867,13 +2743,13 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D50" t="s">
         <v>15</v>
@@ -2884,13 +2760,13 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D51" t="s">
         <v>15</v>
@@ -2901,13 +2777,13 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B52" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C52" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D52" t="s">
         <v>15</v>
@@ -2918,13 +2794,13 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B53" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C53" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D53" t="s">
         <v>15</v>
@@ -2935,13 +2811,13 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>91</v>
       </c>
       <c r="C54" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D54" t="s">
         <v>15</v>
@@ -2952,13 +2828,13 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B55" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C55" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D55" t="s">
         <v>15</v>
@@ -2969,13 +2845,13 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="C56" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="D56" t="s">
         <v>15</v>
@@ -2986,13 +2862,13 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="B57" t="s">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="C57" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="D57" t="s">
         <v>15</v>
@@ -3003,13 +2879,13 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="B58" t="s">
-        <v>177</v>
+        <v>91</v>
       </c>
       <c r="C58" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="D58" t="s">
         <v>15</v>
@@ -3020,13 +2896,13 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="B59" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="C59" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="D59" t="s">
         <v>15</v>
@@ -3037,13 +2913,13 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="B60" t="s">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="C60" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="D60" t="s">
         <v>15</v>
@@ -3054,13 +2930,13 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="B61" t="s">
-        <v>183</v>
+        <v>91</v>
       </c>
       <c r="C61" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="D61" t="s">
         <v>15</v>
@@ -3071,13 +2947,13 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="B62" t="s">
-        <v>185</v>
+        <v>91</v>
       </c>
       <c r="C62" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="D62" t="s">
         <v>15</v>
@@ -3088,13 +2964,13 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B63" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C63" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D63" t="s">
         <v>15</v>
@@ -3105,13 +2981,13 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B64" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C64" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="D64" t="s">
         <v>15</v>
@@ -3122,13 +2998,13 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B65" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C65" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D65" t="s">
         <v>15</v>
@@ -3139,13 +3015,13 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B66" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C66" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D66" t="s">
         <v>15</v>
@@ -3156,13 +3032,13 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B67" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C67" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="D67" t="s">
         <v>15</v>
@@ -3173,13 +3049,13 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C68" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D68" t="s">
         <v>15</v>
@@ -3190,13 +3066,13 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B69" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C69" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D69" t="s">
         <v>15</v>
@@ -3207,13 +3083,13 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B70" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C70" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D70" t="s">
         <v>15</v>
@@ -3224,13 +3100,13 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B71" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C71" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D71" t="s">
         <v>15</v>
@@ -3241,13 +3117,13 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B72" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C72" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D72" t="s">
         <v>15</v>
@@ -3258,13 +3134,13 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B73" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C73" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D73" t="s">
         <v>15</v>
@@ -3275,16 +3151,16 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B74" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C74" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D74" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="G74" t="s">
         <v>12</v>
@@ -3292,16 +3168,16 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B75" t="s">
+        <v>184</v>
+      </c>
+      <c r="C75" t="s">
         <v>193</v>
       </c>
-      <c r="C75" t="s">
-        <v>202</v>
-      </c>
       <c r="D75" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="G75" t="s">
         <v>12</v>
@@ -3309,13 +3185,13 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B76" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C76" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D76" t="s">
         <v>15</v>
@@ -3326,13 +3202,13 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B77" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="C77" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D77" t="s">
         <v>15</v>
@@ -3343,13 +3219,13 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B78" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C78" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D78" t="s">
         <v>15</v>
@@ -3360,13 +3236,13 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B79" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="C79" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D79" t="s">
         <v>15</v>
@@ -3377,13 +3253,13 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C80" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D80" t="s">
         <v>15</v>
@@ -3394,16 +3270,16 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B81" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>202</v>
       </c>
       <c r="G81" t="s">
         <v>12</v>
@@ -3411,16 +3287,16 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B82" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C82" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D82" t="s">
-        <v>15</v>
+        <v>202</v>
       </c>
       <c r="G82" t="s">
         <v>12</v>
@@ -3428,13 +3304,13 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C83" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D83" t="s">
         <v>15</v>
@@ -3445,13 +3321,13 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B84" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C84" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D84" t="s">
         <v>15</v>
@@ -3462,13 +3338,13 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B85" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="C85" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D85" t="s">
         <v>15</v>
@@ -3479,13 +3355,13 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B86" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C86" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D86" t="s">
         <v>15</v>
@@ -3496,13 +3372,13 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B87" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="C87" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D87" t="s">
         <v>15</v>
@@ -3513,13 +3389,13 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B88" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C88" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D88" t="s">
         <v>15</v>
@@ -3530,13 +3406,13 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B89" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C89" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D89" t="s">
         <v>15</v>
@@ -3547,13 +3423,13 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B90" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C90" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D90" t="s">
         <v>15</v>
@@ -3564,13 +3440,13 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B91" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C91" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D91" t="s">
         <v>15</v>
@@ -3581,13 +3457,13 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B92" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="C92" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D92" t="s">
         <v>15</v>
@@ -3598,13 +3474,13 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B93" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C93" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D93" t="s">
         <v>15</v>
@@ -3615,13 +3491,13 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C94" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D94" t="s">
         <v>15</v>
@@ -3632,13 +3508,13 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B95" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="C95" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D95" t="s">
         <v>15</v>
@@ -3649,13 +3525,13 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B96" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C96" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D96" t="s">
         <v>15</v>
@@ -3666,13 +3542,13 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B97" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C97" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D97" t="s">
         <v>15</v>
@@ -3683,13 +3559,13 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B98" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C98" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D98" t="s">
         <v>15</v>
@@ -3700,13 +3576,13 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B99" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C99" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D99" t="s">
         <v>15</v>
@@ -3717,13 +3593,13 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B100" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C100" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D100" t="s">
         <v>15</v>
@@ -3734,13 +3610,13 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B101" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C101" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D101" t="s">
         <v>15</v>
@@ -3751,13 +3627,13 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B102" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="C102" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D102" t="s">
         <v>15</v>
@@ -3768,13 +3644,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B103" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C103" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D103" t="s">
         <v>15</v>
@@ -3785,13 +3661,13 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B104" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C104" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D104" t="s">
         <v>15</v>
@@ -3802,13 +3678,13 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B105" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C105" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D105" t="s">
         <v>15</v>
@@ -3819,13 +3695,13 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B106" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="C106" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D106" t="s">
         <v>15</v>
@@ -3836,13 +3712,13 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B107" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C107" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D107" t="s">
         <v>15</v>
@@ -3853,13 +3729,13 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B108" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C108" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D108" t="s">
         <v>15</v>
@@ -3870,13 +3746,13 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B109" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C109" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D109" t="s">
         <v>15</v>
@@ -3887,13 +3763,13 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B110" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C110" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D110" t="s">
         <v>15</v>
@@ -3904,13 +3780,13 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B111" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C111" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D111" t="s">
         <v>15</v>
@@ -3921,13 +3797,13 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B112" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C112" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D112" t="s">
         <v>15</v>
@@ -3938,13 +3814,13 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B113" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C113" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D113" t="s">
         <v>15</v>
@@ -3955,13 +3831,13 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B114" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C114" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D114" t="s">
         <v>15</v>
@@ -3972,13 +3848,13 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B115" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C115" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D115" t="s">
         <v>15</v>
@@ -3989,13 +3865,13 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B116" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C116" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D116" t="s">
         <v>15</v>
@@ -4006,13 +3882,13 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B117" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C117" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D117" t="s">
         <v>15</v>
@@ -4023,13 +3899,13 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B118" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C118" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D118" t="s">
         <v>15</v>
@@ -4040,13 +3916,13 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B119" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C119" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D119" t="s">
         <v>15</v>
@@ -4057,13 +3933,13 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B120" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C120" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D120" t="s">
         <v>15</v>
@@ -4074,13 +3950,13 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B121" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C121" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D121" t="s">
         <v>15</v>
@@ -4091,13 +3967,13 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B122" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C122" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D122" t="s">
         <v>15</v>
@@ -4108,13 +3984,13 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B123" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="C123" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D123" t="s">
         <v>15</v>
@@ -4125,13 +4001,13 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B124" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C124" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D124" t="s">
         <v>15</v>
@@ -4142,13 +4018,13 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B125" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C125" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D125" t="s">
         <v>15</v>
@@ -4159,13 +4035,13 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B126" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C126" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D126" t="s">
         <v>15</v>
@@ -4176,13 +4052,13 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B127" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C127" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D127" t="s">
         <v>15</v>
@@ -4193,13 +4069,13 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B128" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C128" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D128" t="s">
         <v>15</v>
@@ -4210,13 +4086,13 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B129" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C129" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D129" t="s">
         <v>15</v>
@@ -4227,13 +4103,13 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B130" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C130" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D130" t="s">
         <v>15</v>
@@ -4244,13 +4120,13 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B131" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C131" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D131" t="s">
         <v>15</v>
@@ -4261,13 +4137,13 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B132" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C132" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D132" t="s">
         <v>15</v>
@@ -4278,13 +4154,13 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B133" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C133" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D133" t="s">
         <v>15</v>
@@ -4295,13 +4171,13 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B134" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C134" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D134" t="s">
         <v>15</v>
@@ -4312,13 +4188,13 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B135" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C135" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D135" t="s">
         <v>15</v>
@@ -4329,13 +4205,13 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B136" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C136" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D136" t="s">
         <v>15</v>
@@ -4346,13 +4222,13 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B137" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C137" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D137" t="s">
         <v>15</v>
@@ -4363,13 +4239,13 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B138" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C138" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>15</v>
@@ -4380,13 +4256,13 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B139" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C139" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D139" t="s">
         <v>15</v>
@@ -4397,13 +4273,13 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B140" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C140" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D140" t="s">
         <v>15</v>
@@ -4414,13 +4290,13 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B141" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C141" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
         <v>15</v>
@@ -4431,13 +4307,13 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B142" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C142" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D142" t="s">
         <v>15</v>
@@ -4448,13 +4324,13 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B143" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C143" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D143" t="s">
         <v>15</v>
@@ -4465,13 +4341,13 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B144" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C144" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D144" t="s">
         <v>15</v>
@@ -4482,13 +4358,13 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B145" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C145" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D145" t="s">
         <v>15</v>
@@ -4499,13 +4375,13 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B146" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C146" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D146" t="s">
         <v>15</v>
@@ -4516,13 +4392,13 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B147" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C147" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D147" t="s">
         <v>15</v>
@@ -4533,13 +4409,13 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B148" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C148" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D148" t="s">
         <v>15</v>
@@ -4550,13 +4426,13 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B149" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C149" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D149" t="s">
         <v>15</v>
@@ -4567,13 +4443,13 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B150" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C150" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D150" t="s">
         <v>15</v>
@@ -4584,13 +4460,13 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B151" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C151" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D151" t="s">
         <v>15</v>
@@ -4601,13 +4477,13 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B152" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C152" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D152" t="s">
         <v>15</v>
@@ -4618,13 +4494,13 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B153" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C153" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D153" t="s">
         <v>15</v>
@@ -4635,13 +4511,13 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B154" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C154" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D154" t="s">
         <v>15</v>
@@ -4652,13 +4528,13 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B155" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C155" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D155" t="s">
         <v>15</v>
@@ -4669,13 +4545,13 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B156" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C156" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="D156" t="s">
         <v>15</v>
@@ -4686,13 +4562,13 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B157" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C157" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="D157" t="s">
         <v>15</v>
@@ -4703,13 +4579,13 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B158" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C158" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D158" t="s">
         <v>15</v>
@@ -4720,13 +4596,13 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B159" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C159" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="D159" t="s">
         <v>15</v>
@@ -4737,13 +4613,13 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B160" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C160" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D160" t="s">
         <v>15</v>
@@ -4754,13 +4630,13 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B161" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C161" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D161" t="s">
         <v>15</v>
@@ -4771,13 +4647,13 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B162" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C162" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D162" t="s">
         <v>15</v>
@@ -4788,13 +4664,13 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B163" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C163" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D163" t="s">
         <v>15</v>
@@ -4805,13 +4681,13 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B164" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C164" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D164" t="s">
         <v>15</v>
@@ -4822,13 +4698,13 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B165" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C165" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D165" t="s">
         <v>15</v>
@@ -4839,13 +4715,13 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C166" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D166" t="s">
         <v>15</v>
@@ -4856,13 +4732,13 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B167" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C167" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D167" t="s">
         <v>15</v>
@@ -4873,13 +4749,13 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C168" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="D168" t="s">
         <v>15</v>
@@ -4890,13 +4766,13 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B169" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C169" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D169" t="s">
         <v>15</v>
@@ -4907,13 +4783,13 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B170" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D170" t="s">
         <v>15</v>
@@ -4924,13 +4800,13 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B171" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D171" t="s">
         <v>15</v>
@@ -4941,13 +4817,13 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B172" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C172" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="D172" t="s">
         <v>15</v>
@@ -4958,13 +4834,13 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>302</v>
+        <v>182</v>
       </c>
       <c r="C173" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="D173" t="s">
         <v>15</v>
@@ -4975,13 +4851,13 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C174" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="D174" t="s">
         <v>15</v>
@@ -4992,13 +4868,13 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="C175" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="D175" t="s">
         <v>15</v>
@@ -5009,13 +4885,13 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B176" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C176" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D176" t="s">
         <v>15</v>
@@ -5026,13 +4902,13 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B177" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C177" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="D177" t="s">
         <v>15</v>
@@ -5043,13 +4919,13 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B178" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D178" t="s">
         <v>15</v>
@@ -5060,13 +4936,13 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C179" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D179" t="s">
         <v>15</v>
@@ -5077,13 +4953,13 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B180" t="s">
-        <v>181</v>
+        <v>303</v>
       </c>
       <c r="C180" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D180" t="s">
         <v>15</v>
@@ -5094,13 +4970,13 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B181" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C181" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D181" t="s">
         <v>15</v>
@@ -5111,13 +4987,13 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B182" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C182" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D182" t="s">
         <v>15</v>
@@ -5128,13 +5004,13 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B183" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C183" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D183" t="s">
         <v>15</v>
@@ -5145,13 +5021,13 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B184" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C184" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D184" t="s">
         <v>15</v>
@@ -5162,13 +5038,13 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B185" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C185" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D185" t="s">
         <v>15</v>
@@ -5179,13 +5055,13 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B186" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C186" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D186" t="s">
         <v>15</v>
@@ -5196,13 +5072,13 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B187" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C187" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D187" t="s">
         <v>15</v>
@@ -5213,13 +5089,13 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B188" t="s">
-        <v>302</v>
+        <v>186</v>
       </c>
       <c r="C188" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D188" t="s">
         <v>15</v>
@@ -5230,13 +5106,13 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B189" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C189" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D189" t="s">
         <v>15</v>
@@ -5247,13 +5123,13 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B190" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C190" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D190" t="s">
         <v>15</v>
@@ -5264,13 +5140,13 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B191" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="C191" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D191" t="s">
         <v>15</v>
@@ -5281,13 +5157,13 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B192" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C192" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="D192" t="s">
         <v>15</v>
@@ -5298,13 +5174,13 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B193" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C193" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="D193" t="s">
         <v>15</v>
@@ -5315,13 +5191,13 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="C194" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D194" t="s">
         <v>15</v>
@@ -5332,13 +5208,13 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B195" t="s">
-        <v>193</v>
+        <v>303</v>
       </c>
       <c r="C195" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D195" t="s">
         <v>15</v>
@@ -5349,13 +5225,13 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B196" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C196" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D196" t="s">
         <v>15</v>
@@ -5366,13 +5242,13 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B197" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C197" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D197" t="s">
         <v>15</v>
@@ -5383,13 +5259,13 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B198" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C198" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D198" t="s">
         <v>15</v>
@@ -5400,13 +5276,13 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B199" t="s">
-        <v>329</v>
+        <v>194</v>
       </c>
       <c r="C199" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D199" t="s">
         <v>15</v>
@@ -5417,13 +5293,13 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B200" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="C200" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D200" t="s">
         <v>15</v>
@@ -5434,13 +5310,13 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B201" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C201" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D201" t="s">
         <v>15</v>
@@ -5451,13 +5327,13 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B202" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C202" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D202" t="s">
         <v>15</v>
@@ -5468,13 +5344,13 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B203" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C203" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="D203" t="s">
         <v>15</v>
@@ -5485,13 +5361,13 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B204" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C204" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D204" t="s">
         <v>15</v>
@@ -5502,13 +5378,13 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B205" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="C205" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D205" t="s">
         <v>15</v>
@@ -5519,13 +5395,13 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B206" t="s">
-        <v>175</v>
+        <v>330</v>
       </c>
       <c r="C206" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D206" t="s">
         <v>15</v>
@@ -5536,13 +5412,13 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B207" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C207" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D207" t="s">
         <v>15</v>
@@ -5553,13 +5429,13 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B208" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C208" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D208" t="s">
         <v>15</v>
@@ -5570,13 +5446,13 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B209" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C209" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D209" t="s">
         <v>15</v>
@@ -5587,13 +5463,13 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B210" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C210" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D210" t="s">
         <v>15</v>
@@ -5604,13 +5480,13 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B211" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C211" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D211" t="s">
         <v>15</v>
@@ -5621,13 +5497,13 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B212" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="C212" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D212" t="s">
         <v>15</v>
@@ -5638,13 +5514,13 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B213" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C213" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D213" t="s">
         <v>15</v>
@@ -5655,13 +5531,13 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B214" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C214" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D214" t="s">
         <v>15</v>
@@ -5672,13 +5548,13 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B215" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C215" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D215" t="s">
         <v>15</v>
@@ -5689,13 +5565,13 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B216" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C216" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D216" t="s">
         <v>15</v>
@@ -5706,13 +5582,13 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B217" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C217" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D217" t="s">
         <v>15</v>
@@ -5723,13 +5599,13 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B218" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C218" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D218" t="s">
         <v>15</v>
@@ -5740,13 +5616,13 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B219" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C219" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D219" t="s">
         <v>15</v>
@@ -5757,13 +5633,13 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B220" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C220" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D220" t="s">
         <v>15</v>
@@ -5774,13 +5650,13 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B221" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C221" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D221" t="s">
         <v>15</v>
@@ -5791,13 +5667,13 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B222" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C222" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D222" t="s">
         <v>15</v>
@@ -5808,13 +5684,13 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B223" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C223" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D223" t="s">
         <v>15</v>
@@ -5825,13 +5701,13 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B224" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C224" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D224" t="s">
         <v>15</v>
@@ -5842,13 +5718,13 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B225" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="C225" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D225" t="s">
         <v>15</v>
@@ -5859,13 +5735,13 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B226" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="C226" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D226" t="s">
         <v>15</v>
@@ -5876,13 +5752,13 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B227" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C227" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D227" t="s">
         <v>15</v>
@@ -5893,13 +5769,13 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B228" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C228" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D228" t="s">
         <v>15</v>
@@ -5910,13 +5786,13 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B229" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C229" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D229" t="s">
         <v>15</v>
@@ -5927,13 +5803,13 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B230" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C230" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D230" t="s">
         <v>15</v>
@@ -5944,13 +5820,13 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B231" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C231" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D231" t="s">
         <v>15</v>
@@ -5961,13 +5837,13 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B232" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="C232" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D232" t="s">
         <v>15</v>
@@ -5978,13 +5854,13 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B233" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="C233" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D233" t="s">
         <v>15</v>
@@ -5995,13 +5871,13 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B234" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C234" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="D234" t="s">
         <v>15</v>
@@ -6012,13 +5888,13 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B235" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C235" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D235" t="s">
         <v>15</v>
@@ -6029,13 +5905,13 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B236" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C236" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D236" t="s">
         <v>15</v>
@@ -6046,13 +5922,13 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B237" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C237" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D237" t="s">
         <v>15</v>
@@ -6063,13 +5939,13 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B238" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C238" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D238" t="s">
         <v>15</v>
@@ -6080,13 +5956,13 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B239" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C239" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D239" t="s">
         <v>15</v>
@@ -6097,13 +5973,13 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B240" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C240" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D240" t="s">
         <v>15</v>
@@ -6114,13 +5990,13 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B241" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C241" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D241" t="s">
         <v>15</v>
@@ -6131,13 +6007,13 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B242" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C242" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D242" t="s">
         <v>15</v>
@@ -6148,13 +6024,13 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B243" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C243" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D243" t="s">
         <v>15</v>
@@ -6165,13 +6041,13 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B244" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C244" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D244" t="s">
         <v>15</v>
@@ -6182,141 +6058,120 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="B245" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="C245" t="s">
-        <v>10</v>
+        <v>370</v>
       </c>
       <c r="D245" t="s">
-        <v>11</v>
-      </c>
-      <c r="E245" t="s">
-        <v>11</v>
-      </c>
-      <c r="F245" t="s">
+        <v>15</v>
+      </c>
+      <c r="G245" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="B246" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="C246" t="s">
-        <v>23</v>
+        <v>371</v>
       </c>
       <c r="D246" t="s">
-        <v>24</v>
-      </c>
-      <c r="E246" t="s">
-        <v>24</v>
-      </c>
-      <c r="F246" t="s">
+        <v>15</v>
+      </c>
+      <c r="G246" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="B247" t="s">
-        <v>25</v>
+        <v>184</v>
       </c>
       <c r="C247" t="s">
-        <v>26</v>
+        <v>372</v>
       </c>
       <c r="D247" t="s">
-        <v>27</v>
-      </c>
-      <c r="E247" t="s">
-        <v>404</v>
-      </c>
-      <c r="F247" t="s">
+        <v>15</v>
+      </c>
+      <c r="G247" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="B248" t="s">
-        <v>13</v>
+        <v>182</v>
       </c>
       <c r="C248" t="s">
-        <v>28</v>
+        <v>373</v>
       </c>
       <c r="D248" t="s">
-        <v>29</v>
-      </c>
-      <c r="E248" t="s">
-        <v>29</v>
-      </c>
-      <c r="F248" t="s">
+        <v>15</v>
+      </c>
+      <c r="G248" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="B249" t="s">
-        <v>9</v>
+        <v>184</v>
       </c>
       <c r="C249" t="s">
-        <v>38</v>
+        <v>374</v>
       </c>
       <c r="D249" t="s">
-        <v>39</v>
-      </c>
-      <c r="E249" t="s">
-        <v>39</v>
-      </c>
-      <c r="F249" t="s">
+        <v>15</v>
+      </c>
+      <c r="G249" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="B250" t="s">
-        <v>25</v>
+        <v>174</v>
       </c>
       <c r="C250" t="s">
-        <v>42</v>
+        <v>375</v>
       </c>
       <c r="D250" t="s">
-        <v>27</v>
-      </c>
-      <c r="E250" t="s">
-        <v>27</v>
-      </c>
-      <c r="F250" t="s">
+        <v>15</v>
+      </c>
+      <c r="G250" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>8</v>
+        <v>173</v>
       </c>
       <c r="B251" t="s">
-        <v>9</v>
+        <v>194</v>
       </c>
       <c r="C251" t="s">
-        <v>49</v>
+        <v>376</v>
       </c>
       <c r="D251" t="s">
-        <v>50</v>
-      </c>
-      <c r="E251" t="s">
-        <v>50</v>
-      </c>
-      <c r="F251" t="s">
+        <v>15</v>
+      </c>
+      <c r="G251" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6325,16 +6180,16 @@
         <v>8</v>
       </c>
       <c r="B252" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C252" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D252" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E252" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F252" t="s">
         <v>12</v>
@@ -6345,16 +6200,16 @@
         <v>8</v>
       </c>
       <c r="B253" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C253" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D253" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E253" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F253" t="s">
         <v>12</v>
@@ -6365,16 +6220,16 @@
         <v>8</v>
       </c>
       <c r="B254" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C254" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D254" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E254" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F254" t="s">
         <v>12</v>
@@ -6385,16 +6240,16 @@
         <v>8</v>
       </c>
       <c r="B255" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C255" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="D255" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="E255" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="F255" t="s">
         <v>12</v>
@@ -6405,16 +6260,16 @@
         <v>8</v>
       </c>
       <c r="B256" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C256" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="D256" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E256" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="F256" t="s">
         <v>12</v>
@@ -6425,16 +6280,16 @@
         <v>8</v>
       </c>
       <c r="B257" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="C257" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="D257" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E257" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F257" t="s">
         <v>12</v>
@@ -6445,16 +6300,16 @@
         <v>8</v>
       </c>
       <c r="B258" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="C258" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="D258" t="s">
         <v>27</v>
       </c>
       <c r="E258" t="s">
-        <v>77</v>
+        <v>424</v>
       </c>
       <c r="F258" t="s">
         <v>12</v>
@@ -6465,16 +6320,16 @@
         <v>8</v>
       </c>
       <c r="B259" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="C259" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="D259" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="E259" t="s">
-        <v>84</v>
+        <v>434</v>
       </c>
       <c r="F259" t="s">
         <v>12</v>
@@ -6485,16 +6340,16 @@
         <v>8</v>
       </c>
       <c r="B260" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C260" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="D260" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E260" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F260" t="s">
         <v>12</v>
@@ -6505,16 +6360,16 @@
         <v>8</v>
       </c>
       <c r="B261" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C261" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="D261" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E261" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F261" t="s">
         <v>12</v>
@@ -6522,19 +6377,19 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B262" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="C262" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D262" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E262" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F262" t="s">
         <v>12</v>
@@ -6542,39 +6397,33 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B263" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="C263" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="D263" t="s">
-        <v>11</v>
-      </c>
-      <c r="E263" t="s">
-        <v>11</v>
-      </c>
-      <c r="F263" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B264" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="C264" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="D264" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="E264" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="F264" t="s">
         <v>12</v>
@@ -6582,19 +6431,19 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B265" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="C265" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="D265" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="E265" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
@@ -6602,19 +6451,19 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B266" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="C266" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D266" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E266" t="s">
-        <v>11</v>
+        <v>450</v>
       </c>
       <c r="F266" t="s">
         <v>12</v>
@@ -6622,19 +6471,19 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B267" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="C267" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="D267" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E267" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="F267" t="s">
         <v>12</v>
@@ -6642,19 +6491,19 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B268" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C268" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D268" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E268" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="F268" t="s">
         <v>12</v>
@@ -6662,19 +6511,19 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>8</v>
+      </c>
+      <c r="B269" t="s">
+        <v>25</v>
+      </c>
+      <c r="C269" t="s">
         <v>88</v>
       </c>
-      <c r="B269" t="s">
-        <v>106</v>
-      </c>
-      <c r="C269" t="s">
-        <v>107</v>
-      </c>
       <c r="D269" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="E269" t="s">
-        <v>108</v>
+        <v>468</v>
       </c>
       <c r="F269" t="s">
         <v>12</v>
@@ -6682,19 +6531,19 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B270" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="C270" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="D270" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="E270" t="s">
-        <v>118</v>
+        <v>475</v>
       </c>
       <c r="F270" t="s">
         <v>12</v>
@@ -6702,19 +6551,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B271" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C271" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="D271" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="E271" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="F271" t="s">
         <v>12</v>
@@ -6722,19 +6571,19 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B272" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C272" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D272" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="E272" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="F272" t="s">
         <v>12</v>
@@ -6742,19 +6591,19 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B273" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C273" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="D273" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E273" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="F273" t="s">
         <v>12</v>
@@ -6762,19 +6611,19 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B274" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C274" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="D274" t="s">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="E274" t="s">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="F274" t="s">
         <v>12</v>
@@ -6782,19 +6631,19 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B275" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C275" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="D275" t="s">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="E275" t="s">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="F275" t="s">
         <v>12</v>
@@ -6802,19 +6651,19 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B276" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C276" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="D276" t="s">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="E276" t="s">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="F276" t="s">
         <v>12</v>
@@ -6822,19 +6671,19 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B277" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C277" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="D277" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="E277" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="F277" t="s">
         <v>12</v>
@@ -6842,19 +6691,19 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B278" t="s">
+        <v>98</v>
+      </c>
+      <c r="C278" t="s">
         <v>106</v>
       </c>
-      <c r="C278" t="s">
-        <v>133</v>
-      </c>
       <c r="D278" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="E278" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="F278" t="s">
         <v>12</v>
@@ -6862,19 +6711,19 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B279" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C279" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="D279" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="E279" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="F279" t="s">
         <v>12</v>
@@ -6882,19 +6731,19 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B280" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C280" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="D280" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="E280" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
@@ -6902,19 +6751,19 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B281" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C281" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="D281" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="E281" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="F281" t="s">
         <v>12</v>
@@ -6922,19 +6771,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B282" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C282" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="D282" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="E282" t="s">
-        <v>151</v>
+        <v>470</v>
       </c>
       <c r="F282" t="s">
         <v>12</v>
@@ -6942,19 +6791,19 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B283" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C283" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="D283" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="E283" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F283" t="s">
         <v>12</v>
@@ -6962,19 +6811,19 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B284" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C284" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="D284" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E284" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F284" t="s">
         <v>12</v>
@@ -6982,19 +6831,19 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B285" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C285" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="D285" t="s">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="E285" t="s">
-        <v>161</v>
+        <v>458</v>
       </c>
       <c r="F285" t="s">
         <v>12</v>
@@ -7002,19 +6851,19 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B286" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C286" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="D286" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="E286" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="F286" t="s">
         <v>12</v>
@@ -7022,19 +6871,19 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B287" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C287" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="D287" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="E287" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="F287" t="s">
         <v>12</v>
@@ -7042,352 +6891,379 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B288" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C288" t="s">
+        <v>132</v>
+      </c>
+      <c r="D288" t="s">
+        <v>130</v>
+      </c>
+      <c r="E288" t="s">
+        <v>130</v>
+      </c>
+      <c r="F288" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>90</v>
+      </c>
+      <c r="B289" t="s">
+        <v>111</v>
+      </c>
+      <c r="C289" t="s">
+        <v>133</v>
+      </c>
+      <c r="D289" t="s">
+        <v>130</v>
+      </c>
+      <c r="E289" t="s">
+        <v>130</v>
+      </c>
+      <c r="F289" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>90</v>
+      </c>
+      <c r="B290" t="s">
+        <v>108</v>
+      </c>
+      <c r="C290" t="s">
+        <v>134</v>
+      </c>
+      <c r="D290" t="s">
+        <v>130</v>
+      </c>
+      <c r="E290" t="s">
+        <v>130</v>
+      </c>
+      <c r="F290" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>90</v>
+      </c>
+      <c r="B291" t="s">
+        <v>108</v>
+      </c>
+      <c r="C291" t="s">
+        <v>135</v>
+      </c>
+      <c r="D291" t="s">
+        <v>136</v>
+      </c>
+      <c r="E291" t="s">
+        <v>136</v>
+      </c>
+      <c r="F291" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>90</v>
+      </c>
+      <c r="B292" t="s">
+        <v>108</v>
+      </c>
+      <c r="C292" t="s">
+        <v>139</v>
+      </c>
+      <c r="D292" t="s">
+        <v>140</v>
+      </c>
+      <c r="E292" t="s">
+        <v>140</v>
+      </c>
+      <c r="F292" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>90</v>
+      </c>
+      <c r="B293" t="s">
+        <v>111</v>
+      </c>
+      <c r="C293" t="s">
+        <v>141</v>
+      </c>
+      <c r="D293" t="s">
+        <v>140</v>
+      </c>
+      <c r="E293" t="s">
+        <v>140</v>
+      </c>
+      <c r="F293" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>90</v>
+      </c>
+      <c r="B294" t="s">
+        <v>111</v>
+      </c>
+      <c r="C294" t="s">
+        <v>142</v>
+      </c>
+      <c r="D294" t="s">
+        <v>143</v>
+      </c>
+      <c r="E294" t="s">
+        <v>140</v>
+      </c>
+      <c r="F294" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>90</v>
+      </c>
+      <c r="B295" t="s">
+        <v>111</v>
+      </c>
+      <c r="C295" t="s">
+        <v>144</v>
+      </c>
+      <c r="D295" t="s">
+        <v>143</v>
+      </c>
+      <c r="E295" t="s">
+        <v>140</v>
+      </c>
+      <c r="F295" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>90</v>
+      </c>
+      <c r="B296" t="s">
+        <v>108</v>
+      </c>
+      <c r="C296" t="s">
+        <v>151</v>
+      </c>
+      <c r="D296" t="s">
+        <v>152</v>
+      </c>
+      <c r="E296" t="s">
+        <v>152</v>
+      </c>
+      <c r="F296" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>90</v>
+      </c>
+      <c r="B297" t="s">
+        <v>98</v>
+      </c>
+      <c r="C297" t="s">
+        <v>159</v>
+      </c>
+      <c r="D297" t="s">
+        <v>123</v>
+      </c>
+      <c r="E297" t="s">
+        <v>123</v>
+      </c>
+      <c r="F297" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>90</v>
+      </c>
+      <c r="B298" t="s">
+        <v>98</v>
+      </c>
+      <c r="C298" t="s">
+        <v>160</v>
+      </c>
+      <c r="D298" t="s">
+        <v>123</v>
+      </c>
+      <c r="E298" t="s">
+        <v>123</v>
+      </c>
+      <c r="F298" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>90</v>
+      </c>
+      <c r="B299" t="s">
+        <v>97</v>
+      </c>
+      <c r="C299" t="s">
+        <v>161</v>
+      </c>
+      <c r="D299" t="s">
+        <v>162</v>
+      </c>
+      <c r="E299" t="s">
+        <v>162</v>
+      </c>
+      <c r="F299" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>90</v>
+      </c>
+      <c r="B300" t="s">
+        <v>98</v>
+      </c>
+      <c r="C300" t="s">
+        <v>165</v>
+      </c>
+      <c r="D300" t="s">
+        <v>27</v>
+      </c>
+      <c r="E300" t="s">
+        <v>457</v>
+      </c>
+      <c r="F300" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>90</v>
+      </c>
+      <c r="B301" t="s">
+        <v>111</v>
+      </c>
+      <c r="C301" t="s">
+        <v>167</v>
+      </c>
+      <c r="D301" t="s">
+        <v>152</v>
+      </c>
+      <c r="E301" t="s">
+        <v>152</v>
+      </c>
+      <c r="F301" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>90</v>
+      </c>
+      <c r="B302" t="s">
+        <v>111</v>
+      </c>
+      <c r="C302" t="s">
         <v>168</v>
       </c>
-      <c r="D288" t="s">
-        <v>151</v>
-      </c>
-      <c r="E288" t="s">
-        <v>151</v>
-      </c>
-      <c r="F288" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>88</v>
-      </c>
-      <c r="B289" t="s">
-        <v>109</v>
-      </c>
-      <c r="C289" t="s">
+      <c r="D302" t="s">
+        <v>152</v>
+      </c>
+      <c r="E302" t="s">
+        <v>152</v>
+      </c>
+      <c r="F302" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>90</v>
+      </c>
+      <c r="B303" t="s">
+        <v>111</v>
+      </c>
+      <c r="C303" t="s">
+        <v>169</v>
+      </c>
+      <c r="D303" t="s">
+        <v>152</v>
+      </c>
+      <c r="E303" t="s">
+        <v>152</v>
+      </c>
+      <c r="F303" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>90</v>
+      </c>
+      <c r="B304" t="s">
+        <v>111</v>
+      </c>
+      <c r="C304" t="s">
         <v>170</v>
       </c>
-      <c r="D289" t="s">
+      <c r="D304" t="s">
         <v>118</v>
       </c>
-      <c r="E289" t="s">
-        <v>118</v>
-      </c>
-      <c r="F289" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
-        <v>88</v>
-      </c>
-      <c r="B290" t="s">
-        <v>109</v>
-      </c>
-      <c r="C290" t="s">
+      <c r="E304" t="s">
+        <v>120</v>
+      </c>
+      <c r="F304" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>90</v>
+      </c>
+      <c r="B305" t="s">
+        <v>111</v>
+      </c>
+      <c r="C305" t="s">
         <v>171</v>
       </c>
-      <c r="D290" t="s">
-        <v>118</v>
-      </c>
-      <c r="E290" t="s">
-        <v>11</v>
-      </c>
-      <c r="F290" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
-        <v>8</v>
-      </c>
-      <c r="B291" t="s">
-        <v>20</v>
-      </c>
-      <c r="C291" t="s">
-        <v>21</v>
-      </c>
-      <c r="D291" t="s">
-        <v>15</v>
-      </c>
-      <c r="G291" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A292" t="s">
-        <v>8</v>
-      </c>
-      <c r="B292" t="s">
-        <v>30</v>
-      </c>
-      <c r="C292" t="s">
-        <v>32</v>
-      </c>
-      <c r="D292" t="s">
-        <v>15</v>
-      </c>
-      <c r="G292" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A293" t="s">
-        <v>8</v>
-      </c>
-      <c r="B293" t="s">
-        <v>9</v>
-      </c>
-      <c r="C293" t="s">
-        <v>35</v>
-      </c>
-      <c r="D293" t="s">
-        <v>36</v>
-      </c>
-      <c r="E293" t="s">
-        <v>422</v>
-      </c>
-      <c r="F293" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>8</v>
-      </c>
-      <c r="B294" t="s">
-        <v>40</v>
-      </c>
-      <c r="C294" t="s">
-        <v>41</v>
-      </c>
-      <c r="D294" t="s">
-        <v>15</v>
-      </c>
-      <c r="G294" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>8</v>
-      </c>
-      <c r="B295" t="s">
-        <v>18</v>
-      </c>
-      <c r="C295" t="s">
-        <v>48</v>
-      </c>
-      <c r="D295" t="s">
-        <v>15</v>
-      </c>
-      <c r="G295" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>8</v>
-      </c>
-      <c r="B296" t="s">
-        <v>25</v>
-      </c>
-      <c r="C296" t="s">
-        <v>67</v>
-      </c>
-      <c r="D296" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>88</v>
-      </c>
-      <c r="B297" t="s">
-        <v>96</v>
-      </c>
-      <c r="C297" t="s">
-        <v>104</v>
-      </c>
-      <c r="D297" t="s">
-        <v>103</v>
-      </c>
-      <c r="E297" t="s">
-        <v>103</v>
-      </c>
-      <c r="F297" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>88</v>
-      </c>
-      <c r="B298" t="s">
-        <v>109</v>
-      </c>
-      <c r="C298" t="s">
-        <v>110</v>
-      </c>
-      <c r="D298" t="s">
+      <c r="D305" t="s">
+        <v>120</v>
+      </c>
+      <c r="E305" t="s">
+        <v>120</v>
+      </c>
+      <c r="F305" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>90</v>
+      </c>
+      <c r="B306" t="s">
         <v>111</v>
       </c>
-      <c r="E298" t="s">
-        <v>111</v>
-      </c>
-      <c r="F298" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>88</v>
-      </c>
-      <c r="B299" t="s">
-        <v>106</v>
-      </c>
-      <c r="C299" t="s">
-        <v>112</v>
-      </c>
-      <c r="D299" t="s">
-        <v>111</v>
-      </c>
-      <c r="E299" t="s">
-        <v>111</v>
-      </c>
-      <c r="F299" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
-        <v>88</v>
-      </c>
-      <c r="B300" t="s">
-        <v>109</v>
-      </c>
-      <c r="C300" t="s">
-        <v>141</v>
-      </c>
-      <c r="D300" t="s">
-        <v>142</v>
-      </c>
-      <c r="E300" t="s">
-        <v>139</v>
-      </c>
-      <c r="F300" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>88</v>
-      </c>
-      <c r="B301" t="s">
-        <v>109</v>
-      </c>
-      <c r="C301" t="s">
-        <v>143</v>
-      </c>
-      <c r="D301" t="s">
-        <v>142</v>
-      </c>
-      <c r="E301" t="s">
-        <v>139</v>
-      </c>
-      <c r="F301" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>88</v>
-      </c>
-      <c r="B302" t="s">
-        <v>89</v>
-      </c>
-      <c r="C302" t="s">
-        <v>146</v>
-      </c>
-      <c r="D302" t="s">
-        <v>15</v>
-      </c>
-      <c r="G302" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>88</v>
-      </c>
-      <c r="B303" t="s">
-        <v>89</v>
-      </c>
-      <c r="C303" t="s">
-        <v>162</v>
-      </c>
-      <c r="D303" t="s">
-        <v>15</v>
-      </c>
-      <c r="G303" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>88</v>
-      </c>
-      <c r="B304" t="s">
-        <v>96</v>
-      </c>
-      <c r="C304" t="s">
-        <v>164</v>
-      </c>
-      <c r="D304" t="s">
-        <v>27</v>
-      </c>
-      <c r="E304" t="s">
-        <v>27</v>
-      </c>
-      <c r="F304" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>88</v>
-      </c>
-      <c r="B305" t="s">
-        <v>89</v>
-      </c>
-      <c r="C305" t="s">
-        <v>165</v>
-      </c>
-      <c r="D305" t="s">
-        <v>15</v>
-      </c>
-      <c r="G305" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>88</v>
-      </c>
-      <c r="B306" t="s">
-        <v>109</v>
-      </c>
       <c r="C306" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D306" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E306" t="s">
-        <v>118</v>
+        <v>470</v>
       </c>
       <c r="F306" t="s">
         <v>12</v>
@@ -7413,7 +7289,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A117"/>
+  <dimension ref="A1:A126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -7423,47 +7299,47 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -7473,122 +7349,122 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>404</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -7633,12 +7509,12 @@
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>201</v>
+        <v>413</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>413</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
@@ -7673,22 +7549,22 @@
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>129</v>
+        <v>420</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>420</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>135</v>
+        <v>421</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>421</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
@@ -7698,52 +7574,52 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>423</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>36</v>
+        <v>429</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
@@ -7753,67 +7629,67 @@
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>431</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>29</v>
+        <v>442</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
@@ -7823,12 +7699,12 @@
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>121</v>
+        <v>444</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>444</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
@@ -7838,7 +7714,7 @@
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
@@ -7848,122 +7724,122 @@
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>447</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>161</v>
+        <v>76</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>77</v>
+        <v>449</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>450</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>451</v>
+        <v>162</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>452</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>453</v>
+        <v>87</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>151</v>
+        <v>460</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>118</v>
+        <v>464</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
@@ -7973,32 +7849,77 @@
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>466</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>142</v>
+        <v>469</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>470</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -8008,542 +7929,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>474</v>
-      </c>
-      <c r="C4" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>476</v>
-      </c>
-      <c r="C6" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>477</v>
-      </c>
-      <c r="C7" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>478</v>
-      </c>
-      <c r="C8" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>479</v>
-      </c>
-      <c r="C9" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>480</v>
-      </c>
-      <c r="C10" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>481</v>
-      </c>
-      <c r="C11" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>482</v>
-      </c>
-      <c r="C12" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>483</v>
-      </c>
-      <c r="C13" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>484</v>
-      </c>
-      <c r="C14" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>485</v>
-      </c>
-      <c r="C15" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
-        <v>486</v>
-      </c>
-      <c r="C16" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>487</v>
-      </c>
-      <c r="C17" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
-        <v>488</v>
-      </c>
-      <c r="C18" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>489</v>
-      </c>
-      <c r="C19" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>491</v>
-      </c>
-      <c r="C20" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>493</v>
-      </c>
-      <c r="C21" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>494</v>
-      </c>
-      <c r="C22" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>495</v>
-      </c>
-      <c r="C23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" t="s">
-        <v>496</v>
-      </c>
-      <c r="C24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" t="s">
-        <v>497</v>
-      </c>
-      <c r="C25" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" t="s">
-        <v>498</v>
-      </c>
-      <c r="C26" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" t="s">
-        <v>499</v>
-      </c>
-      <c r="C27" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
-        <v>500</v>
-      </c>
-      <c r="C28" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" t="s">
-        <v>501</v>
-      </c>
-      <c r="C29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" t="s">
-        <v>502</v>
-      </c>
-      <c r="C30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" t="s">
-        <v>503</v>
-      </c>
-      <c r="C31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" t="s">
-        <v>504</v>
-      </c>
-      <c r="C32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" t="s">
-        <v>505</v>
-      </c>
-      <c r="C33" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" t="s">
-        <v>506</v>
-      </c>
-      <c r="C34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" t="s">
-        <v>507</v>
-      </c>
-      <c r="C35" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" t="s">
-        <v>508</v>
-      </c>
-      <c r="C36" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" t="s">
-        <v>509</v>
-      </c>
-      <c r="C37" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" t="s">
-        <v>160</v>
-      </c>
-      <c r="C38" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" t="s">
-        <v>510</v>
-      </c>
-      <c r="C39" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" t="s">
-        <v>511</v>
-      </c>
-      <c r="C40" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" t="s">
-        <v>512</v>
-      </c>
-      <c r="C41" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>88</v>
-      </c>
-      <c r="B42" t="s">
-        <v>513</v>
-      </c>
-      <c r="C42" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>88</v>
-      </c>
-      <c r="B43" t="s">
-        <v>514</v>
-      </c>
-      <c r="C43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44" t="s">
-        <v>515</v>
-      </c>
-      <c r="C44" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" t="s">
-        <v>516</v>
-      </c>
-      <c r="C45" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" t="s">
-        <v>517</v>
-      </c>
-      <c r="C46" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>88</v>
-      </c>
-      <c r="B47" t="s">
-        <v>518</v>
-      </c>
-      <c r="C47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8553,7 +7938,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>519</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -8561,50 +7946,50 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>520</v>
+        <v>479</v>
       </c>
       <c r="B3" t="s">
-        <v>521</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>522</v>
+        <v>481</v>
       </c>
       <c r="B4" t="s">
-        <v>523</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>524</v>
+        <v>483</v>
       </c>
       <c r="B5" t="s">
-        <v>525</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>526</v>
+        <v>485</v>
       </c>
       <c r="B6" t="s">
-        <v>527</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>528</v>
+        <v>487</v>
       </c>
       <c r="B7" t="s">
-        <v>529</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>530</v>
+        <v>489</v>
       </c>
       <c r="B8" t="s">
-        <v>531</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -8612,42 +7997,42 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="B10" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="B11" t="s">
-        <v>534</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="B12" t="s">
-        <v>535</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="B13" t="s">
-        <v>536</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="B14" t="s">
-        <v>537</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
